--- a/TEST - SP 2026 - predtekmovanje - rezultati - Copy.xlsx
+++ b/TEST - SP 2026 - predtekmovanje - rezultati - Copy.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00630992-A6F5-49B5-B26D-C495FF7CC0D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30" yWindow="0" windowWidth="28770" windowHeight="17070" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -902,14 +902,41 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -930,33 +957,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1241,7 +1241,7 @@
   <dimension ref="A1:DS300"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" style="47" customWidth="1"/>
+    <col min="1" max="1" width="4.85546875" style="32" customWidth="1"/>
     <col min="2" max="2" width="17.140625" customWidth="1"/>
     <col min="3" max="3" width="7.5703125" style="8" customWidth="1"/>
     <col min="4" max="4" width="5.140625" bestFit="1" customWidth="1"/>
@@ -1257,115 +1257,115 @@
       <c r="D1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="32" t="s">
+      <c r="E1" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="33"/>
-      <c r="G1" s="32" t="s">
+      <c r="F1" s="39"/>
+      <c r="G1" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="33"/>
-      <c r="I1" s="32" t="s">
+      <c r="H1" s="39"/>
+      <c r="I1" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="35"/>
-      <c r="K1" s="35"/>
-      <c r="L1" s="35"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="32" t="s">
+      <c r="J1" s="38"/>
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
+      <c r="M1" s="39"/>
+      <c r="N1" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="O1" s="35"/>
-      <c r="P1" s="35"/>
-      <c r="Q1" s="33"/>
-      <c r="R1" s="32" t="s">
+      <c r="O1" s="38"/>
+      <c r="P1" s="38"/>
+      <c r="Q1" s="39"/>
+      <c r="R1" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="S1" s="35"/>
-      <c r="T1" s="33"/>
-      <c r="U1" s="32" t="s">
+      <c r="S1" s="38"/>
+      <c r="T1" s="39"/>
+      <c r="U1" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="V1" s="35"/>
-      <c r="W1" s="35"/>
-      <c r="X1" s="35"/>
-      <c r="Y1" s="33"/>
-      <c r="Z1" s="32" t="s">
+      <c r="V1" s="38"/>
+      <c r="W1" s="38"/>
+      <c r="X1" s="38"/>
+      <c r="Y1" s="39"/>
+      <c r="Z1" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="AA1" s="35"/>
-      <c r="AB1" s="35"/>
-      <c r="AC1" s="33"/>
-      <c r="AD1" s="32" t="s">
+      <c r="AA1" s="38"/>
+      <c r="AB1" s="38"/>
+      <c r="AC1" s="39"/>
+      <c r="AD1" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="AE1" s="35"/>
-      <c r="AF1" s="33"/>
-      <c r="AG1" s="32" t="s">
+      <c r="AE1" s="38"/>
+      <c r="AF1" s="39"/>
+      <c r="AG1" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="AH1" s="35"/>
-      <c r="AI1" s="35"/>
-      <c r="AJ1" s="35"/>
-      <c r="AK1" s="33"/>
-      <c r="AL1" s="32" t="s">
+      <c r="AH1" s="38"/>
+      <c r="AI1" s="38"/>
+      <c r="AJ1" s="38"/>
+      <c r="AK1" s="39"/>
+      <c r="AL1" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="AM1" s="35"/>
-      <c r="AN1" s="35"/>
-      <c r="AO1" s="33"/>
-      <c r="AP1" s="32" t="s">
+      <c r="AM1" s="38"/>
+      <c r="AN1" s="38"/>
+      <c r="AO1" s="39"/>
+      <c r="AP1" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="AQ1" s="35"/>
-      <c r="AR1" s="35"/>
-      <c r="AS1" s="33"/>
-      <c r="AT1" s="32" t="s">
+      <c r="AQ1" s="38"/>
+      <c r="AR1" s="38"/>
+      <c r="AS1" s="39"/>
+      <c r="AT1" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="AU1" s="35"/>
-      <c r="AV1" s="35"/>
-      <c r="AW1" s="33"/>
-      <c r="AX1" s="32" t="s">
+      <c r="AU1" s="38"/>
+      <c r="AV1" s="38"/>
+      <c r="AW1" s="39"/>
+      <c r="AX1" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="AY1" s="35"/>
-      <c r="AZ1" s="35"/>
-      <c r="BA1" s="33"/>
-      <c r="BB1" s="32" t="s">
+      <c r="AY1" s="38"/>
+      <c r="AZ1" s="38"/>
+      <c r="BA1" s="39"/>
+      <c r="BB1" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="BC1" s="35"/>
-      <c r="BD1" s="35"/>
-      <c r="BE1" s="35"/>
-      <c r="BF1" s="35"/>
-      <c r="BG1" s="33"/>
-      <c r="BH1" s="32" t="s">
+      <c r="BC1" s="38"/>
+      <c r="BD1" s="38"/>
+      <c r="BE1" s="38"/>
+      <c r="BF1" s="38"/>
+      <c r="BG1" s="39"/>
+      <c r="BH1" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="BI1" s="35"/>
-      <c r="BJ1" s="35"/>
-      <c r="BK1" s="35"/>
-      <c r="BL1" s="35"/>
-      <c r="BM1" s="33"/>
-      <c r="BN1" s="32" t="s">
+      <c r="BI1" s="38"/>
+      <c r="BJ1" s="38"/>
+      <c r="BK1" s="38"/>
+      <c r="BL1" s="38"/>
+      <c r="BM1" s="39"/>
+      <c r="BN1" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="BO1" s="35"/>
-      <c r="BP1" s="35"/>
-      <c r="BQ1" s="35"/>
-      <c r="BR1" s="35"/>
-      <c r="BS1" s="33"/>
-      <c r="BT1" s="32" t="s">
+      <c r="BO1" s="38"/>
+      <c r="BP1" s="38"/>
+      <c r="BQ1" s="38"/>
+      <c r="BR1" s="38"/>
+      <c r="BS1" s="39"/>
+      <c r="BT1" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="BU1" s="35"/>
-      <c r="BV1" s="35"/>
-      <c r="BW1" s="33"/>
+      <c r="BU1" s="38"/>
+      <c r="BV1" s="38"/>
+      <c r="BW1" s="39"/>
       <c r="BX1" s="9"/>
     </row>
     <row r="2" spans="1:123" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="48" t="s">
+      <c r="A2" s="33" t="s">
         <v>18</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -1590,81 +1590,81 @@
       <c r="BW2" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="BX2" s="45" t="s">
+      <c r="BX2" s="40" t="s">
         <v>93</v>
       </c>
-      <c r="BY2" s="35"/>
-      <c r="BZ2" s="35"/>
-      <c r="CA2" s="33"/>
-      <c r="CB2" s="36" t="s">
+      <c r="BY2" s="38"/>
+      <c r="BZ2" s="38"/>
+      <c r="CA2" s="39"/>
+      <c r="CB2" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="CC2" s="35"/>
-      <c r="CD2" s="35"/>
-      <c r="CE2" s="33"/>
-      <c r="CF2" s="37" t="s">
+      <c r="CC2" s="38"/>
+      <c r="CD2" s="38"/>
+      <c r="CE2" s="39"/>
+      <c r="CF2" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="CG2" s="35"/>
-      <c r="CH2" s="35"/>
-      <c r="CI2" s="33"/>
-      <c r="CJ2" s="46" t="s">
+      <c r="CG2" s="38"/>
+      <c r="CH2" s="38"/>
+      <c r="CI2" s="39"/>
+      <c r="CJ2" s="41" t="s">
         <v>96</v>
       </c>
-      <c r="CK2" s="35"/>
-      <c r="CL2" s="35"/>
-      <c r="CM2" s="33"/>
-      <c r="CN2" s="38" t="s">
+      <c r="CK2" s="38"/>
+      <c r="CL2" s="38"/>
+      <c r="CM2" s="39"/>
+      <c r="CN2" s="47" t="s">
         <v>97</v>
       </c>
-      <c r="CO2" s="35"/>
-      <c r="CP2" s="35"/>
-      <c r="CQ2" s="33"/>
-      <c r="CR2" s="39" t="s">
+      <c r="CO2" s="38"/>
+      <c r="CP2" s="38"/>
+      <c r="CQ2" s="39"/>
+      <c r="CR2" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="CS2" s="35"/>
-      <c r="CT2" s="35"/>
-      <c r="CU2" s="33"/>
-      <c r="CV2" s="43" t="s">
+      <c r="CS2" s="38"/>
+      <c r="CT2" s="38"/>
+      <c r="CU2" s="39"/>
+      <c r="CV2" s="42" t="s">
         <v>99</v>
       </c>
-      <c r="CW2" s="35"/>
-      <c r="CX2" s="35"/>
-      <c r="CY2" s="33"/>
-      <c r="CZ2" s="40" t="s">
+      <c r="CW2" s="38"/>
+      <c r="CX2" s="38"/>
+      <c r="CY2" s="39"/>
+      <c r="CZ2" s="49" t="s">
         <v>100</v>
       </c>
-      <c r="DA2" s="35"/>
-      <c r="DB2" s="35"/>
-      <c r="DC2" s="33"/>
-      <c r="DD2" s="41" t="s">
+      <c r="DA2" s="38"/>
+      <c r="DB2" s="38"/>
+      <c r="DC2" s="39"/>
+      <c r="DD2" s="50" t="s">
         <v>101</v>
       </c>
-      <c r="DE2" s="35"/>
-      <c r="DF2" s="35"/>
-      <c r="DG2" s="33"/>
-      <c r="DH2" s="44" t="s">
+      <c r="DE2" s="38"/>
+      <c r="DF2" s="38"/>
+      <c r="DG2" s="39"/>
+      <c r="DH2" s="43" t="s">
         <v>102</v>
       </c>
-      <c r="DI2" s="35"/>
-      <c r="DJ2" s="35"/>
-      <c r="DK2" s="33"/>
-      <c r="DL2" s="42" t="s">
+      <c r="DI2" s="38"/>
+      <c r="DJ2" s="38"/>
+      <c r="DK2" s="39"/>
+      <c r="DL2" s="51" t="s">
         <v>103</v>
       </c>
-      <c r="DM2" s="35"/>
-      <c r="DN2" s="35"/>
-      <c r="DO2" s="33"/>
-      <c r="DP2" s="34" t="s">
+      <c r="DM2" s="38"/>
+      <c r="DN2" s="38"/>
+      <c r="DO2" s="39"/>
+      <c r="DP2" s="44" t="s">
         <v>95</v>
       </c>
-      <c r="DQ2" s="35"/>
-      <c r="DR2" s="35"/>
-      <c r="DS2" s="33"/>
+      <c r="DQ2" s="38"/>
+      <c r="DR2" s="38"/>
+      <c r="DS2" s="39"/>
     </row>
     <row r="3" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="49"/>
+      <c r="A3" s="34"/>
       <c r="B3" s="10" t="s">
         <v>104</v>
       </c>
@@ -1804,7 +1804,7 @@
       <c r="DS3" s="13"/>
     </row>
     <row r="4" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="50"/>
+      <c r="A4" s="35"/>
       <c r="B4" s="14" t="s">
         <v>105</v>
       </c>
@@ -1944,7 +1944,7 @@
       <c r="DS4" s="17"/>
     </row>
     <row r="5" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="50"/>
+      <c r="A5" s="35"/>
       <c r="B5" s="14" t="s">
         <v>106</v>
       </c>
@@ -2084,7 +2084,7 @@
       <c r="DS5" s="17"/>
     </row>
     <row r="6" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="50"/>
+      <c r="A6" s="35"/>
       <c r="B6" s="14" t="s">
         <v>107</v>
       </c>
@@ -2224,7 +2224,7 @@
       <c r="DS6" s="17"/>
     </row>
     <row r="7" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="50"/>
+      <c r="A7" s="35"/>
       <c r="B7" s="24" t="s">
         <v>108</v>
       </c>
@@ -2364,7 +2364,7 @@
       <c r="DS7" s="17"/>
     </row>
     <row r="8" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="50"/>
+      <c r="A8" s="35"/>
       <c r="B8" s="24" t="s">
         <v>109</v>
       </c>
@@ -2504,7 +2504,7 @@
       <c r="DS8" s="17"/>
     </row>
     <row r="9" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="50"/>
+      <c r="A9" s="35"/>
       <c r="B9" s="14" t="s">
         <v>110</v>
       </c>
@@ -2644,7 +2644,7 @@
       <c r="DS9" s="17"/>
     </row>
     <row r="10" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="50"/>
+      <c r="A10" s="35"/>
       <c r="B10" s="14"/>
       <c r="C10" s="30">
         <f t="shared" si="0"/>
@@ -2772,7 +2772,7 @@
       <c r="DS10" s="17"/>
     </row>
     <row r="11" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="50"/>
+      <c r="A11" s="35"/>
       <c r="B11" s="14"/>
       <c r="C11" s="30">
         <f t="shared" si="0"/>
@@ -2900,7 +2900,7 @@
       <c r="DS11" s="17"/>
     </row>
     <row r="12" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="50"/>
+      <c r="A12" s="35"/>
       <c r="B12" s="14"/>
       <c r="C12" s="30">
         <f t="shared" si="0"/>
@@ -3028,7 +3028,7 @@
       <c r="DS12" s="17"/>
     </row>
     <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="50"/>
+      <c r="A13" s="35"/>
       <c r="B13" s="14"/>
       <c r="C13" s="30">
         <f t="shared" si="0"/>
@@ -3156,7 +3156,7 @@
       <c r="DS13" s="17"/>
     </row>
     <row r="14" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="50"/>
+      <c r="A14" s="35"/>
       <c r="B14" s="14"/>
       <c r="C14" s="30">
         <f t="shared" si="0"/>
@@ -3284,7 +3284,7 @@
       <c r="DS14" s="17"/>
     </row>
     <row r="15" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="50"/>
+      <c r="A15" s="35"/>
       <c r="B15" s="14"/>
       <c r="C15" s="30">
         <f t="shared" si="0"/>
@@ -3412,7 +3412,7 @@
       <c r="DS15" s="17"/>
     </row>
     <row r="16" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="50"/>
+      <c r="A16" s="35"/>
       <c r="B16" s="14"/>
       <c r="C16" s="30">
         <f t="shared" si="0"/>
@@ -3540,7 +3540,7 @@
       <c r="DS16" s="17"/>
     </row>
     <row r="17" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="50"/>
+      <c r="A17" s="35"/>
       <c r="B17" s="14"/>
       <c r="C17" s="30">
         <f t="shared" si="0"/>
@@ -3668,7 +3668,7 @@
       <c r="DS17" s="17"/>
     </row>
     <row r="18" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="50"/>
+      <c r="A18" s="35"/>
       <c r="B18" s="14"/>
       <c r="C18" s="30">
         <f t="shared" si="0"/>
@@ -3796,7 +3796,7 @@
       <c r="DS18" s="17"/>
     </row>
     <row r="19" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="50"/>
+      <c r="A19" s="35"/>
       <c r="B19" s="14"/>
       <c r="C19" s="30">
         <f t="shared" si="0"/>
@@ -3924,7 +3924,7 @@
       <c r="DS19" s="17"/>
     </row>
     <row r="20" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="50"/>
+      <c r="A20" s="35"/>
       <c r="B20" s="14"/>
       <c r="C20" s="30">
         <f t="shared" si="0"/>
@@ -4052,7 +4052,7 @@
       <c r="DS20" s="17"/>
     </row>
     <row r="21" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="50"/>
+      <c r="A21" s="35"/>
       <c r="B21" s="14"/>
       <c r="C21" s="30">
         <f t="shared" si="0"/>
@@ -4180,7 +4180,7 @@
       <c r="DS21" s="17"/>
     </row>
     <row r="22" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="50"/>
+      <c r="A22" s="35"/>
       <c r="B22" s="14"/>
       <c r="C22" s="30">
         <f t="shared" si="0"/>
@@ -4308,7 +4308,7 @@
       <c r="DS22" s="17"/>
     </row>
     <row r="23" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="50"/>
+      <c r="A23" s="35"/>
       <c r="B23" s="14"/>
       <c r="C23" s="30">
         <f t="shared" si="0"/>
@@ -4436,7 +4436,7 @@
       <c r="DS23" s="17"/>
     </row>
     <row r="24" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="50"/>
+      <c r="A24" s="35"/>
       <c r="B24" s="14"/>
       <c r="C24" s="30">
         <f t="shared" si="0"/>
@@ -4564,7 +4564,7 @@
       <c r="DS24" s="17"/>
     </row>
     <row r="25" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="50"/>
+      <c r="A25" s="35"/>
       <c r="B25" s="14"/>
       <c r="C25" s="30">
         <f t="shared" si="0"/>
@@ -4692,7 +4692,7 @@
       <c r="DS25" s="17"/>
     </row>
     <row r="26" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="50"/>
+      <c r="A26" s="35"/>
       <c r="B26" s="14"/>
       <c r="C26" s="30">
         <f t="shared" si="0"/>
@@ -4820,7 +4820,7 @@
       <c r="DS26" s="17"/>
     </row>
     <row r="27" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="50"/>
+      <c r="A27" s="35"/>
       <c r="B27" s="14"/>
       <c r="C27" s="30">
         <f t="shared" si="0"/>
@@ -4948,7 +4948,7 @@
       <c r="DS27" s="17"/>
     </row>
     <row r="28" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="50"/>
+      <c r="A28" s="35"/>
       <c r="B28" s="14"/>
       <c r="C28" s="30">
         <f t="shared" si="0"/>
@@ -5076,7 +5076,7 @@
       <c r="DS28" s="17"/>
     </row>
     <row r="29" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="50"/>
+      <c r="A29" s="35"/>
       <c r="B29" s="14"/>
       <c r="C29" s="30">
         <f t="shared" si="0"/>
@@ -5204,7 +5204,7 @@
       <c r="DS29" s="17"/>
     </row>
     <row r="30" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="50"/>
+      <c r="A30" s="35"/>
       <c r="B30" s="14"/>
       <c r="C30" s="30">
         <f t="shared" si="0"/>
@@ -5332,7 +5332,7 @@
       <c r="DS30" s="17"/>
     </row>
     <row r="31" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="50"/>
+      <c r="A31" s="35"/>
       <c r="B31" s="14"/>
       <c r="C31" s="30">
         <f t="shared" si="0"/>
@@ -5460,7 +5460,7 @@
       <c r="DS31" s="17"/>
     </row>
     <row r="32" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="50"/>
+      <c r="A32" s="35"/>
       <c r="B32" s="14"/>
       <c r="C32" s="30">
         <f t="shared" si="0"/>
@@ -5588,7 +5588,7 @@
       <c r="DS32" s="17"/>
     </row>
     <row r="33" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="50"/>
+      <c r="A33" s="35"/>
       <c r="B33" s="14"/>
       <c r="C33" s="30">
         <f t="shared" si="0"/>
@@ -5716,7 +5716,7 @@
       <c r="DS33" s="17"/>
     </row>
     <row r="34" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="50"/>
+      <c r="A34" s="35"/>
       <c r="B34" s="14"/>
       <c r="C34" s="30">
         <f t="shared" si="0"/>
@@ -5844,7 +5844,7 @@
       <c r="DS34" s="17"/>
     </row>
     <row r="35" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="50"/>
+      <c r="A35" s="35"/>
       <c r="B35" s="14"/>
       <c r="C35" s="30">
         <f t="shared" si="0"/>
@@ -5972,7 +5972,7 @@
       <c r="DS35" s="17"/>
     </row>
     <row r="36" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="50"/>
+      <c r="A36" s="35"/>
       <c r="B36" s="14"/>
       <c r="C36" s="30">
         <f t="shared" si="0"/>
@@ -6100,7 +6100,7 @@
       <c r="DS36" s="17"/>
     </row>
     <row r="37" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="50"/>
+      <c r="A37" s="35"/>
       <c r="B37" s="14"/>
       <c r="C37" s="30">
         <f t="shared" si="0"/>
@@ -6228,7 +6228,7 @@
       <c r="DS37" s="17"/>
     </row>
     <row r="38" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="50"/>
+      <c r="A38" s="35"/>
       <c r="B38" s="14"/>
       <c r="C38" s="30">
         <f t="shared" si="0"/>
@@ -6356,7 +6356,7 @@
       <c r="DS38" s="17"/>
     </row>
     <row r="39" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="50"/>
+      <c r="A39" s="35"/>
       <c r="B39" s="14"/>
       <c r="C39" s="30">
         <f t="shared" si="0"/>
@@ -6484,7 +6484,7 @@
       <c r="DS39" s="17"/>
     </row>
     <row r="40" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="50"/>
+      <c r="A40" s="35"/>
       <c r="B40" s="14"/>
       <c r="C40" s="30">
         <f t="shared" si="0"/>
@@ -6612,7 +6612,7 @@
       <c r="DS40" s="17"/>
     </row>
     <row r="41" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="50"/>
+      <c r="A41" s="35"/>
       <c r="B41" s="14"/>
       <c r="C41" s="30">
         <f t="shared" si="0"/>
@@ -6740,7 +6740,7 @@
       <c r="DS41" s="17"/>
     </row>
     <row r="42" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="50"/>
+      <c r="A42" s="35"/>
       <c r="B42" s="14"/>
       <c r="C42" s="30">
         <f t="shared" si="0"/>
@@ -6868,7 +6868,7 @@
       <c r="DS42" s="17"/>
     </row>
     <row r="43" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="50"/>
+      <c r="A43" s="35"/>
       <c r="B43" s="14"/>
       <c r="C43" s="30">
         <f t="shared" si="0"/>
@@ -6996,7 +6996,7 @@
       <c r="DS43" s="17"/>
     </row>
     <row r="44" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="50"/>
+      <c r="A44" s="35"/>
       <c r="B44" s="14"/>
       <c r="C44" s="30">
         <f t="shared" si="0"/>
@@ -7124,7 +7124,7 @@
       <c r="DS44" s="17"/>
     </row>
     <row r="45" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="50"/>
+      <c r="A45" s="35"/>
       <c r="B45" s="14"/>
       <c r="C45" s="30">
         <f t="shared" si="0"/>
@@ -7252,7 +7252,7 @@
       <c r="DS45" s="17"/>
     </row>
     <row r="46" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="50"/>
+      <c r="A46" s="35"/>
       <c r="B46" s="14"/>
       <c r="C46" s="30">
         <f t="shared" si="0"/>
@@ -7380,7 +7380,7 @@
       <c r="DS46" s="17"/>
     </row>
     <row r="47" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="50"/>
+      <c r="A47" s="35"/>
       <c r="B47" s="14"/>
       <c r="C47" s="30">
         <f t="shared" si="0"/>
@@ -7508,7 +7508,7 @@
       <c r="DS47" s="17"/>
     </row>
     <row r="48" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="50"/>
+      <c r="A48" s="35"/>
       <c r="B48" s="14"/>
       <c r="C48" s="30">
         <f t="shared" si="0"/>
@@ -7636,7 +7636,7 @@
       <c r="DS48" s="17"/>
     </row>
     <row r="49" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="50"/>
+      <c r="A49" s="35"/>
       <c r="B49" s="14"/>
       <c r="C49" s="30">
         <f t="shared" si="0"/>
@@ -7764,7 +7764,7 @@
       <c r="DS49" s="17"/>
     </row>
     <row r="50" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="50"/>
+      <c r="A50" s="35"/>
       <c r="B50" s="14"/>
       <c r="C50" s="30">
         <f t="shared" si="0"/>
@@ -7892,7 +7892,7 @@
       <c r="DS50" s="17"/>
     </row>
     <row r="51" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="50"/>
+      <c r="A51" s="35"/>
       <c r="B51" s="14"/>
       <c r="C51" s="30">
         <f t="shared" si="0"/>
@@ -8020,7 +8020,7 @@
       <c r="DS51" s="17"/>
     </row>
     <row r="52" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="50"/>
+      <c r="A52" s="35"/>
       <c r="B52" s="14"/>
       <c r="C52" s="30">
         <f t="shared" si="0"/>
@@ -8148,7 +8148,7 @@
       <c r="DS52" s="17"/>
     </row>
     <row r="53" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="50"/>
+      <c r="A53" s="35"/>
       <c r="B53" s="14"/>
       <c r="C53" s="30">
         <f t="shared" si="0"/>
@@ -8276,7 +8276,7 @@
       <c r="DS53" s="17"/>
     </row>
     <row r="54" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="50"/>
+      <c r="A54" s="35"/>
       <c r="B54" s="14"/>
       <c r="C54" s="30">
         <f t="shared" si="0"/>
@@ -8404,7 +8404,7 @@
       <c r="DS54" s="17"/>
     </row>
     <row r="55" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="50"/>
+      <c r="A55" s="35"/>
       <c r="B55" s="14"/>
       <c r="C55" s="30">
         <f t="shared" si="0"/>
@@ -8532,7 +8532,7 @@
       <c r="DS55" s="17"/>
     </row>
     <row r="56" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="50"/>
+      <c r="A56" s="35"/>
       <c r="B56" s="14"/>
       <c r="C56" s="30">
         <f t="shared" si="0"/>
@@ -8660,7 +8660,7 @@
       <c r="DS56" s="17"/>
     </row>
     <row r="57" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="50"/>
+      <c r="A57" s="35"/>
       <c r="B57" s="14"/>
       <c r="C57" s="30">
         <f t="shared" si="0"/>
@@ -8788,7 +8788,7 @@
       <c r="DS57" s="17"/>
     </row>
     <row r="58" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="50"/>
+      <c r="A58" s="35"/>
       <c r="B58" s="14"/>
       <c r="C58" s="30">
         <f t="shared" si="0"/>
@@ -8916,7 +8916,7 @@
       <c r="DS58" s="17"/>
     </row>
     <row r="59" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="50"/>
+      <c r="A59" s="35"/>
       <c r="B59" s="14"/>
       <c r="C59" s="30">
         <f t="shared" si="0"/>
@@ -9044,7 +9044,7 @@
       <c r="DS59" s="17"/>
     </row>
     <row r="60" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="50"/>
+      <c r="A60" s="35"/>
       <c r="B60" s="14"/>
       <c r="C60" s="30">
         <f t="shared" si="0"/>
@@ -9172,7 +9172,7 @@
       <c r="DS60" s="17"/>
     </row>
     <row r="61" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="50"/>
+      <c r="A61" s="35"/>
       <c r="B61" s="14"/>
       <c r="C61" s="30">
         <f t="shared" si="0"/>
@@ -9300,7 +9300,7 @@
       <c r="DS61" s="17"/>
     </row>
     <row r="62" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="50"/>
+      <c r="A62" s="35"/>
       <c r="B62" s="14"/>
       <c r="C62" s="30">
         <f t="shared" si="0"/>
@@ -9428,7 +9428,7 @@
       <c r="DS62" s="17"/>
     </row>
     <row r="63" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="50"/>
+      <c r="A63" s="35"/>
       <c r="B63" s="14"/>
       <c r="C63" s="30">
         <f t="shared" si="0"/>
@@ -9556,7 +9556,7 @@
       <c r="DS63" s="17"/>
     </row>
     <row r="64" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="50"/>
+      <c r="A64" s="35"/>
       <c r="B64" s="14"/>
       <c r="C64" s="30">
         <f t="shared" si="0"/>
@@ -9684,7 +9684,7 @@
       <c r="DS64" s="17"/>
     </row>
     <row r="65" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="50"/>
+      <c r="A65" s="35"/>
       <c r="B65" s="14"/>
       <c r="C65" s="30">
         <f t="shared" si="0"/>
@@ -9812,7 +9812,7 @@
       <c r="DS65" s="17"/>
     </row>
     <row r="66" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="50"/>
+      <c r="A66" s="35"/>
       <c r="B66" s="14"/>
       <c r="C66" s="30">
         <f t="shared" si="0"/>
@@ -9940,7 +9940,7 @@
       <c r="DS66" s="17"/>
     </row>
     <row r="67" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="50"/>
+      <c r="A67" s="35"/>
       <c r="B67" s="14"/>
       <c r="C67" s="30">
         <f t="shared" si="0"/>
@@ -10068,7 +10068,7 @@
       <c r="DS67" s="17"/>
     </row>
     <row r="68" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="50"/>
+      <c r="A68" s="35"/>
       <c r="B68" s="14"/>
       <c r="C68" s="30">
         <f t="shared" ref="C68:C131" si="1">SUM(D68:DS68)</f>
@@ -10196,7 +10196,7 @@
       <c r="DS68" s="17"/>
     </row>
     <row r="69" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="50"/>
+      <c r="A69" s="35"/>
       <c r="B69" s="14"/>
       <c r="C69" s="30">
         <f t="shared" si="1"/>
@@ -10324,7 +10324,7 @@
       <c r="DS69" s="17"/>
     </row>
     <row r="70" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="50"/>
+      <c r="A70" s="35"/>
       <c r="B70" s="14"/>
       <c r="C70" s="30">
         <f t="shared" si="1"/>
@@ -10452,7 +10452,7 @@
       <c r="DS70" s="17"/>
     </row>
     <row r="71" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="50"/>
+      <c r="A71" s="35"/>
       <c r="B71" s="14"/>
       <c r="C71" s="30">
         <f t="shared" si="1"/>
@@ -10580,7 +10580,7 @@
       <c r="DS71" s="17"/>
     </row>
     <row r="72" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="50"/>
+      <c r="A72" s="35"/>
       <c r="B72" s="14"/>
       <c r="C72" s="30">
         <f t="shared" si="1"/>
@@ -10708,7 +10708,7 @@
       <c r="DS72" s="17"/>
     </row>
     <row r="73" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="50"/>
+      <c r="A73" s="35"/>
       <c r="B73" s="14"/>
       <c r="C73" s="30">
         <f t="shared" si="1"/>
@@ -10836,7 +10836,7 @@
       <c r="DS73" s="17"/>
     </row>
     <row r="74" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="50"/>
+      <c r="A74" s="35"/>
       <c r="B74" s="14"/>
       <c r="C74" s="30">
         <f t="shared" si="1"/>
@@ -10964,7 +10964,7 @@
       <c r="DS74" s="17"/>
     </row>
     <row r="75" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="50"/>
+      <c r="A75" s="35"/>
       <c r="B75" s="14"/>
       <c r="C75" s="30">
         <f t="shared" si="1"/>
@@ -11092,7 +11092,7 @@
       <c r="DS75" s="17"/>
     </row>
     <row r="76" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="50"/>
+      <c r="A76" s="35"/>
       <c r="B76" s="14"/>
       <c r="C76" s="30">
         <f t="shared" si="1"/>
@@ -11220,7 +11220,7 @@
       <c r="DS76" s="17"/>
     </row>
     <row r="77" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="50"/>
+      <c r="A77" s="35"/>
       <c r="B77" s="14"/>
       <c r="C77" s="30">
         <f t="shared" si="1"/>
@@ -11348,7 +11348,7 @@
       <c r="DS77" s="17"/>
     </row>
     <row r="78" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="50"/>
+      <c r="A78" s="35"/>
       <c r="B78" s="14"/>
       <c r="C78" s="30">
         <f t="shared" si="1"/>
@@ -11476,7 +11476,7 @@
       <c r="DS78" s="17"/>
     </row>
     <row r="79" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="50"/>
+      <c r="A79" s="35"/>
       <c r="B79" s="14"/>
       <c r="C79" s="30">
         <f t="shared" si="1"/>
@@ -11604,7 +11604,7 @@
       <c r="DS79" s="17"/>
     </row>
     <row r="80" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="50"/>
+      <c r="A80" s="35"/>
       <c r="B80" s="14"/>
       <c r="C80" s="30">
         <f t="shared" si="1"/>
@@ -11732,7 +11732,7 @@
       <c r="DS80" s="17"/>
     </row>
     <row r="81" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="50"/>
+      <c r="A81" s="35"/>
       <c r="B81" s="14"/>
       <c r="C81" s="30">
         <f t="shared" si="1"/>
@@ -11860,7 +11860,7 @@
       <c r="DS81" s="17"/>
     </row>
     <row r="82" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="50"/>
+      <c r="A82" s="35"/>
       <c r="B82" s="14"/>
       <c r="C82" s="30">
         <f t="shared" si="1"/>
@@ -11988,7 +11988,7 @@
       <c r="DS82" s="17"/>
     </row>
     <row r="83" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="50"/>
+      <c r="A83" s="35"/>
       <c r="B83" s="14"/>
       <c r="C83" s="30">
         <f t="shared" si="1"/>
@@ -12116,7 +12116,7 @@
       <c r="DS83" s="17"/>
     </row>
     <row r="84" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="50"/>
+      <c r="A84" s="35"/>
       <c r="B84" s="14"/>
       <c r="C84" s="30">
         <f t="shared" si="1"/>
@@ -12244,7 +12244,7 @@
       <c r="DS84" s="17"/>
     </row>
     <row r="85" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="50"/>
+      <c r="A85" s="35"/>
       <c r="B85" s="14"/>
       <c r="C85" s="30">
         <f t="shared" si="1"/>
@@ -12372,7 +12372,7 @@
       <c r="DS85" s="17"/>
     </row>
     <row r="86" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="50"/>
+      <c r="A86" s="35"/>
       <c r="B86" s="14"/>
       <c r="C86" s="30">
         <f t="shared" si="1"/>
@@ -12500,7 +12500,7 @@
       <c r="DS86" s="17"/>
     </row>
     <row r="87" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="50"/>
+      <c r="A87" s="35"/>
       <c r="B87" s="14"/>
       <c r="C87" s="30">
         <f t="shared" si="1"/>
@@ -12628,7 +12628,7 @@
       <c r="DS87" s="17"/>
     </row>
     <row r="88" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="50"/>
+      <c r="A88" s="35"/>
       <c r="B88" s="14"/>
       <c r="C88" s="30">
         <f t="shared" si="1"/>
@@ -12756,7 +12756,7 @@
       <c r="DS88" s="17"/>
     </row>
     <row r="89" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="50"/>
+      <c r="A89" s="35"/>
       <c r="B89" s="14"/>
       <c r="C89" s="30">
         <f t="shared" si="1"/>
@@ -12884,7 +12884,7 @@
       <c r="DS89" s="17"/>
     </row>
     <row r="90" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="50"/>
+      <c r="A90" s="35"/>
       <c r="B90" s="14"/>
       <c r="C90" s="30">
         <f t="shared" si="1"/>
@@ -13012,7 +13012,7 @@
       <c r="DS90" s="17"/>
     </row>
     <row r="91" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="50"/>
+      <c r="A91" s="35"/>
       <c r="B91" s="14"/>
       <c r="C91" s="30">
         <f t="shared" si="1"/>
@@ -13140,7 +13140,7 @@
       <c r="DS91" s="17"/>
     </row>
     <row r="92" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="50"/>
+      <c r="A92" s="35"/>
       <c r="B92" s="14"/>
       <c r="C92" s="30">
         <f t="shared" si="1"/>
@@ -13268,7 +13268,7 @@
       <c r="DS92" s="17"/>
     </row>
     <row r="93" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="50"/>
+      <c r="A93" s="35"/>
       <c r="B93" s="14"/>
       <c r="C93" s="30">
         <f t="shared" si="1"/>
@@ -13396,7 +13396,7 @@
       <c r="DS93" s="17"/>
     </row>
     <row r="94" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="50"/>
+      <c r="A94" s="35"/>
       <c r="B94" s="14"/>
       <c r="C94" s="30">
         <f t="shared" si="1"/>
@@ -13524,7 +13524,7 @@
       <c r="DS94" s="17"/>
     </row>
     <row r="95" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="50"/>
+      <c r="A95" s="35"/>
       <c r="B95" s="14"/>
       <c r="C95" s="30">
         <f t="shared" si="1"/>
@@ -13652,7 +13652,7 @@
       <c r="DS95" s="17"/>
     </row>
     <row r="96" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="50"/>
+      <c r="A96" s="35"/>
       <c r="B96" s="14"/>
       <c r="C96" s="30">
         <f t="shared" si="1"/>
@@ -13780,7 +13780,7 @@
       <c r="DS96" s="17"/>
     </row>
     <row r="97" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="50"/>
+      <c r="A97" s="35"/>
       <c r="B97" s="14"/>
       <c r="C97" s="30">
         <f t="shared" si="1"/>
@@ -13908,7 +13908,7 @@
       <c r="DS97" s="17"/>
     </row>
     <row r="98" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="50"/>
+      <c r="A98" s="35"/>
       <c r="B98" s="14"/>
       <c r="C98" s="30">
         <f t="shared" si="1"/>
@@ -14036,7 +14036,7 @@
       <c r="DS98" s="17"/>
     </row>
     <row r="99" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="50"/>
+      <c r="A99" s="35"/>
       <c r="B99" s="14"/>
       <c r="C99" s="30">
         <f t="shared" si="1"/>
@@ -14164,7 +14164,7 @@
       <c r="DS99" s="17"/>
     </row>
     <row r="100" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="50"/>
+      <c r="A100" s="35"/>
       <c r="B100" s="14"/>
       <c r="C100" s="30">
         <f t="shared" si="1"/>
@@ -14292,7 +14292,7 @@
       <c r="DS100" s="17"/>
     </row>
     <row r="101" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="50"/>
+      <c r="A101" s="35"/>
       <c r="B101" s="14"/>
       <c r="C101" s="30">
         <f t="shared" si="1"/>
@@ -14420,7 +14420,7 @@
       <c r="DS101" s="17"/>
     </row>
     <row r="102" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="50"/>
+      <c r="A102" s="35"/>
       <c r="B102" s="14"/>
       <c r="C102" s="30">
         <f t="shared" si="1"/>
@@ -14548,7 +14548,7 @@
       <c r="DS102" s="17"/>
     </row>
     <row r="103" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="50"/>
+      <c r="A103" s="35"/>
       <c r="B103" s="14"/>
       <c r="C103" s="30">
         <f t="shared" si="1"/>
@@ -14676,7 +14676,7 @@
       <c r="DS103" s="17"/>
     </row>
     <row r="104" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="50"/>
+      <c r="A104" s="35"/>
       <c r="B104" s="14"/>
       <c r="C104" s="30">
         <f t="shared" si="1"/>
@@ -14804,7 +14804,7 @@
       <c r="DS104" s="17"/>
     </row>
     <row r="105" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="50"/>
+      <c r="A105" s="35"/>
       <c r="B105" s="14"/>
       <c r="C105" s="30">
         <f t="shared" si="1"/>
@@ -14932,7 +14932,7 @@
       <c r="DS105" s="17"/>
     </row>
     <row r="106" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="50"/>
+      <c r="A106" s="35"/>
       <c r="B106" s="14"/>
       <c r="C106" s="30">
         <f t="shared" si="1"/>
@@ -15060,7 +15060,7 @@
       <c r="DS106" s="17"/>
     </row>
     <row r="107" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="50"/>
+      <c r="A107" s="35"/>
       <c r="B107" s="14"/>
       <c r="C107" s="30">
         <f t="shared" si="1"/>
@@ -15188,7 +15188,7 @@
       <c r="DS107" s="17"/>
     </row>
     <row r="108" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="50"/>
+      <c r="A108" s="35"/>
       <c r="B108" s="14"/>
       <c r="C108" s="30">
         <f t="shared" si="1"/>
@@ -15316,7 +15316,7 @@
       <c r="DS108" s="17"/>
     </row>
     <row r="109" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="50"/>
+      <c r="A109" s="35"/>
       <c r="B109" s="14"/>
       <c r="C109" s="30">
         <f t="shared" si="1"/>
@@ -15444,7 +15444,7 @@
       <c r="DS109" s="17"/>
     </row>
     <row r="110" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="50"/>
+      <c r="A110" s="35"/>
       <c r="B110" s="14"/>
       <c r="C110" s="30">
         <f t="shared" si="1"/>
@@ -15572,7 +15572,7 @@
       <c r="DS110" s="17"/>
     </row>
     <row r="111" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="50"/>
+      <c r="A111" s="35"/>
       <c r="B111" s="14"/>
       <c r="C111" s="30">
         <f t="shared" si="1"/>
@@ -15700,7 +15700,7 @@
       <c r="DS111" s="17"/>
     </row>
     <row r="112" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="50"/>
+      <c r="A112" s="35"/>
       <c r="B112" s="14"/>
       <c r="C112" s="30">
         <f t="shared" si="1"/>
@@ -15828,7 +15828,7 @@
       <c r="DS112" s="17"/>
     </row>
     <row r="113" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="50"/>
+      <c r="A113" s="35"/>
       <c r="B113" s="14"/>
       <c r="C113" s="30">
         <f t="shared" si="1"/>
@@ -15956,7 +15956,7 @@
       <c r="DS113" s="17"/>
     </row>
     <row r="114" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="50"/>
+      <c r="A114" s="35"/>
       <c r="B114" s="14"/>
       <c r="C114" s="30">
         <f t="shared" si="1"/>
@@ -16084,7 +16084,7 @@
       <c r="DS114" s="17"/>
     </row>
     <row r="115" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="50"/>
+      <c r="A115" s="35"/>
       <c r="B115" s="14"/>
       <c r="C115" s="30">
         <f t="shared" si="1"/>
@@ -16212,7 +16212,7 @@
       <c r="DS115" s="17"/>
     </row>
     <row r="116" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="50"/>
+      <c r="A116" s="35"/>
       <c r="B116" s="14"/>
       <c r="C116" s="30">
         <f t="shared" si="1"/>
@@ -16340,7 +16340,7 @@
       <c r="DS116" s="17"/>
     </row>
     <row r="117" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="50"/>
+      <c r="A117" s="35"/>
       <c r="B117" s="14"/>
       <c r="C117" s="30">
         <f t="shared" si="1"/>
@@ -16468,7 +16468,7 @@
       <c r="DS117" s="17"/>
     </row>
     <row r="118" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="50"/>
+      <c r="A118" s="35"/>
       <c r="B118" s="14"/>
       <c r="C118" s="30">
         <f t="shared" si="1"/>
@@ -16596,7 +16596,7 @@
       <c r="DS118" s="17"/>
     </row>
     <row r="119" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="50"/>
+      <c r="A119" s="35"/>
       <c r="B119" s="14"/>
       <c r="C119" s="30">
         <f t="shared" si="1"/>
@@ -16724,7 +16724,7 @@
       <c r="DS119" s="17"/>
     </row>
     <row r="120" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="50"/>
+      <c r="A120" s="35"/>
       <c r="B120" s="14"/>
       <c r="C120" s="30">
         <f t="shared" si="1"/>
@@ -16852,7 +16852,7 @@
       <c r="DS120" s="17"/>
     </row>
     <row r="121" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="50"/>
+      <c r="A121" s="35"/>
       <c r="B121" s="14"/>
       <c r="C121" s="30">
         <f t="shared" si="1"/>
@@ -16980,7 +16980,7 @@
       <c r="DS121" s="17"/>
     </row>
     <row r="122" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="50"/>
+      <c r="A122" s="35"/>
       <c r="B122" s="14"/>
       <c r="C122" s="30">
         <f t="shared" si="1"/>
@@ -17108,7 +17108,7 @@
       <c r="DS122" s="17"/>
     </row>
     <row r="123" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="50"/>
+      <c r="A123" s="35"/>
       <c r="B123" s="14"/>
       <c r="C123" s="30">
         <f t="shared" si="1"/>
@@ -17236,7 +17236,7 @@
       <c r="DS123" s="17"/>
     </row>
     <row r="124" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="50"/>
+      <c r="A124" s="35"/>
       <c r="B124" s="14"/>
       <c r="C124" s="30">
         <f t="shared" si="1"/>
@@ -17364,7 +17364,7 @@
       <c r="DS124" s="17"/>
     </row>
     <row r="125" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="50"/>
+      <c r="A125" s="35"/>
       <c r="B125" s="14"/>
       <c r="C125" s="30">
         <f t="shared" si="1"/>
@@ -17492,7 +17492,7 @@
       <c r="DS125" s="17"/>
     </row>
     <row r="126" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="50"/>
+      <c r="A126" s="35"/>
       <c r="B126" s="14"/>
       <c r="C126" s="30">
         <f t="shared" si="1"/>
@@ -17620,7 +17620,7 @@
       <c r="DS126" s="17"/>
     </row>
     <row r="127" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="50"/>
+      <c r="A127" s="35"/>
       <c r="B127" s="14"/>
       <c r="C127" s="30">
         <f t="shared" si="1"/>
@@ -17748,7 +17748,7 @@
       <c r="DS127" s="17"/>
     </row>
     <row r="128" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="50"/>
+      <c r="A128" s="35"/>
       <c r="B128" s="14"/>
       <c r="C128" s="30">
         <f t="shared" si="1"/>
@@ -17876,7 +17876,7 @@
       <c r="DS128" s="17"/>
     </row>
     <row r="129" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="50"/>
+      <c r="A129" s="35"/>
       <c r="B129" s="14"/>
       <c r="C129" s="30">
         <f t="shared" si="1"/>
@@ -18004,7 +18004,7 @@
       <c r="DS129" s="17"/>
     </row>
     <row r="130" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="50"/>
+      <c r="A130" s="35"/>
       <c r="B130" s="14"/>
       <c r="C130" s="30">
         <f t="shared" si="1"/>
@@ -18132,7 +18132,7 @@
       <c r="DS130" s="17"/>
     </row>
     <row r="131" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="50"/>
+      <c r="A131" s="35"/>
       <c r="B131" s="14"/>
       <c r="C131" s="30">
         <f t="shared" si="1"/>
@@ -18260,7 +18260,7 @@
       <c r="DS131" s="17"/>
     </row>
     <row r="132" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="50"/>
+      <c r="A132" s="35"/>
       <c r="B132" s="14"/>
       <c r="C132" s="30">
         <f t="shared" ref="C132:C195" si="2">SUM(D132:DS132)</f>
@@ -18388,7 +18388,7 @@
       <c r="DS132" s="17"/>
     </row>
     <row r="133" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="50"/>
+      <c r="A133" s="35"/>
       <c r="B133" s="14"/>
       <c r="C133" s="30">
         <f t="shared" si="2"/>
@@ -18516,7 +18516,7 @@
       <c r="DS133" s="17"/>
     </row>
     <row r="134" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="50"/>
+      <c r="A134" s="35"/>
       <c r="B134" s="14"/>
       <c r="C134" s="30">
         <f t="shared" si="2"/>
@@ -18644,7 +18644,7 @@
       <c r="DS134" s="17"/>
     </row>
     <row r="135" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="50"/>
+      <c r="A135" s="35"/>
       <c r="B135" s="14"/>
       <c r="C135" s="30">
         <f t="shared" si="2"/>
@@ -18772,7 +18772,7 @@
       <c r="DS135" s="17"/>
     </row>
     <row r="136" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="50"/>
+      <c r="A136" s="35"/>
       <c r="B136" s="14"/>
       <c r="C136" s="30">
         <f t="shared" si="2"/>
@@ -18900,7 +18900,7 @@
       <c r="DS136" s="17"/>
     </row>
     <row r="137" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A137" s="50"/>
+      <c r="A137" s="35"/>
       <c r="B137" s="14"/>
       <c r="C137" s="30">
         <f t="shared" si="2"/>
@@ -19028,7 +19028,7 @@
       <c r="DS137" s="17"/>
     </row>
     <row r="138" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A138" s="50"/>
+      <c r="A138" s="35"/>
       <c r="B138" s="14"/>
       <c r="C138" s="30">
         <f t="shared" si="2"/>
@@ -19156,7 +19156,7 @@
       <c r="DS138" s="17"/>
     </row>
     <row r="139" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="50"/>
+      <c r="A139" s="35"/>
       <c r="B139" s="14"/>
       <c r="C139" s="30">
         <f t="shared" si="2"/>
@@ -19284,7 +19284,7 @@
       <c r="DS139" s="17"/>
     </row>
     <row r="140" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="50"/>
+      <c r="A140" s="35"/>
       <c r="B140" s="14"/>
       <c r="C140" s="30">
         <f t="shared" si="2"/>
@@ -19412,7 +19412,7 @@
       <c r="DS140" s="17"/>
     </row>
     <row r="141" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="50"/>
+      <c r="A141" s="35"/>
       <c r="B141" s="14"/>
       <c r="C141" s="30">
         <f t="shared" si="2"/>
@@ -19540,7 +19540,7 @@
       <c r="DS141" s="17"/>
     </row>
     <row r="142" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A142" s="50"/>
+      <c r="A142" s="35"/>
       <c r="B142" s="14"/>
       <c r="C142" s="30">
         <f t="shared" si="2"/>
@@ -19668,7 +19668,7 @@
       <c r="DS142" s="17"/>
     </row>
     <row r="143" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="50"/>
+      <c r="A143" s="35"/>
       <c r="B143" s="14"/>
       <c r="C143" s="30">
         <f t="shared" si="2"/>
@@ -19796,7 +19796,7 @@
       <c r="DS143" s="17"/>
     </row>
     <row r="144" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="50"/>
+      <c r="A144" s="35"/>
       <c r="B144" s="14"/>
       <c r="C144" s="30">
         <f t="shared" si="2"/>
@@ -19924,7 +19924,7 @@
       <c r="DS144" s="17"/>
     </row>
     <row r="145" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="50"/>
+      <c r="A145" s="35"/>
       <c r="B145" s="14"/>
       <c r="C145" s="30">
         <f t="shared" si="2"/>
@@ -20052,7 +20052,7 @@
       <c r="DS145" s="17"/>
     </row>
     <row r="146" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A146" s="50"/>
+      <c r="A146" s="35"/>
       <c r="B146" s="14"/>
       <c r="C146" s="30">
         <f t="shared" si="2"/>
@@ -20180,7 +20180,7 @@
       <c r="DS146" s="17"/>
     </row>
     <row r="147" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="50"/>
+      <c r="A147" s="35"/>
       <c r="B147" s="14"/>
       <c r="C147" s="30">
         <f t="shared" si="2"/>
@@ -20308,7 +20308,7 @@
       <c r="DS147" s="17"/>
     </row>
     <row r="148" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="50"/>
+      <c r="A148" s="35"/>
       <c r="B148" s="14"/>
       <c r="C148" s="30">
         <f t="shared" si="2"/>
@@ -20436,7 +20436,7 @@
       <c r="DS148" s="17"/>
     </row>
     <row r="149" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="50"/>
+      <c r="A149" s="35"/>
       <c r="B149" s="14"/>
       <c r="C149" s="30">
         <f t="shared" si="2"/>
@@ -20564,7 +20564,7 @@
       <c r="DS149" s="17"/>
     </row>
     <row r="150" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A150" s="50"/>
+      <c r="A150" s="35"/>
       <c r="B150" s="14"/>
       <c r="C150" s="30">
         <f t="shared" si="2"/>
@@ -20692,7 +20692,7 @@
       <c r="DS150" s="17"/>
     </row>
     <row r="151" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="50"/>
+      <c r="A151" s="35"/>
       <c r="B151" s="14"/>
       <c r="C151" s="30">
         <f t="shared" si="2"/>
@@ -20820,7 +20820,7 @@
       <c r="DS151" s="17"/>
     </row>
     <row r="152" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="50"/>
+      <c r="A152" s="35"/>
       <c r="B152" s="14"/>
       <c r="C152" s="30">
         <f t="shared" si="2"/>
@@ -20948,7 +20948,7 @@
       <c r="DS152" s="17"/>
     </row>
     <row r="153" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="50"/>
+      <c r="A153" s="35"/>
       <c r="B153" s="14"/>
       <c r="C153" s="30">
         <f t="shared" si="2"/>
@@ -21076,7 +21076,7 @@
       <c r="DS153" s="17"/>
     </row>
     <row r="154" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A154" s="50"/>
+      <c r="A154" s="35"/>
       <c r="B154" s="14"/>
       <c r="C154" s="30">
         <f t="shared" si="2"/>
@@ -21204,7 +21204,7 @@
       <c r="DS154" s="17"/>
     </row>
     <row r="155" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="50"/>
+      <c r="A155" s="35"/>
       <c r="B155" s="14"/>
       <c r="C155" s="30">
         <f t="shared" si="2"/>
@@ -21332,7 +21332,7 @@
       <c r="DS155" s="17"/>
     </row>
     <row r="156" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A156" s="50"/>
+      <c r="A156" s="35"/>
       <c r="B156" s="14"/>
       <c r="C156" s="30">
         <f t="shared" si="2"/>
@@ -21460,7 +21460,7 @@
       <c r="DS156" s="17"/>
     </row>
     <row r="157" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A157" s="50"/>
+      <c r="A157" s="35"/>
       <c r="B157" s="14"/>
       <c r="C157" s="30">
         <f t="shared" si="2"/>
@@ -21588,7 +21588,7 @@
       <c r="DS157" s="17"/>
     </row>
     <row r="158" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="50"/>
+      <c r="A158" s="35"/>
       <c r="B158" s="14"/>
       <c r="C158" s="30">
         <f t="shared" si="2"/>
@@ -21716,7 +21716,7 @@
       <c r="DS158" s="17"/>
     </row>
     <row r="159" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A159" s="50"/>
+      <c r="A159" s="35"/>
       <c r="B159" s="14"/>
       <c r="C159" s="30">
         <f t="shared" si="2"/>
@@ -21844,7 +21844,7 @@
       <c r="DS159" s="17"/>
     </row>
     <row r="160" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A160" s="50"/>
+      <c r="A160" s="35"/>
       <c r="B160" s="14"/>
       <c r="C160" s="30">
         <f t="shared" si="2"/>
@@ -21972,7 +21972,7 @@
       <c r="DS160" s="17"/>
     </row>
     <row r="161" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A161" s="50"/>
+      <c r="A161" s="35"/>
       <c r="B161" s="14"/>
       <c r="C161" s="30">
         <f t="shared" si="2"/>
@@ -22100,7 +22100,7 @@
       <c r="DS161" s="17"/>
     </row>
     <row r="162" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A162" s="50"/>
+      <c r="A162" s="35"/>
       <c r="B162" s="14"/>
       <c r="C162" s="30">
         <f t="shared" si="2"/>
@@ -22228,7 +22228,7 @@
       <c r="DS162" s="17"/>
     </row>
     <row r="163" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A163" s="50"/>
+      <c r="A163" s="35"/>
       <c r="B163" s="14"/>
       <c r="C163" s="30">
         <f t="shared" si="2"/>
@@ -22356,7 +22356,7 @@
       <c r="DS163" s="17"/>
     </row>
     <row r="164" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A164" s="50"/>
+      <c r="A164" s="35"/>
       <c r="B164" s="14"/>
       <c r="C164" s="30">
         <f t="shared" si="2"/>
@@ -22484,7 +22484,7 @@
       <c r="DS164" s="17"/>
     </row>
     <row r="165" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A165" s="50"/>
+      <c r="A165" s="35"/>
       <c r="B165" s="14"/>
       <c r="C165" s="30">
         <f t="shared" si="2"/>
@@ -22612,7 +22612,7 @@
       <c r="DS165" s="17"/>
     </row>
     <row r="166" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A166" s="50"/>
+      <c r="A166" s="35"/>
       <c r="B166" s="14"/>
       <c r="C166" s="30">
         <f t="shared" si="2"/>
@@ -22740,7 +22740,7 @@
       <c r="DS166" s="17"/>
     </row>
     <row r="167" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="50"/>
+      <c r="A167" s="35"/>
       <c r="B167" s="14"/>
       <c r="C167" s="30">
         <f t="shared" si="2"/>
@@ -22868,7 +22868,7 @@
       <c r="DS167" s="17"/>
     </row>
     <row r="168" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A168" s="50"/>
+      <c r="A168" s="35"/>
       <c r="B168" s="14"/>
       <c r="C168" s="30">
         <f t="shared" si="2"/>
@@ -22996,7 +22996,7 @@
       <c r="DS168" s="17"/>
     </row>
     <row r="169" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="50"/>
+      <c r="A169" s="35"/>
       <c r="B169" s="14"/>
       <c r="C169" s="30">
         <f t="shared" si="2"/>
@@ -23124,7 +23124,7 @@
       <c r="DS169" s="17"/>
     </row>
     <row r="170" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A170" s="50"/>
+      <c r="A170" s="35"/>
       <c r="B170" s="14"/>
       <c r="C170" s="30">
         <f t="shared" si="2"/>
@@ -23252,7 +23252,7 @@
       <c r="DS170" s="17"/>
     </row>
     <row r="171" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A171" s="50"/>
+      <c r="A171" s="35"/>
       <c r="B171" s="14"/>
       <c r="C171" s="30">
         <f t="shared" si="2"/>
@@ -23380,7 +23380,7 @@
       <c r="DS171" s="17"/>
     </row>
     <row r="172" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A172" s="50"/>
+      <c r="A172" s="35"/>
       <c r="B172" s="14"/>
       <c r="C172" s="30">
         <f t="shared" si="2"/>
@@ -23508,7 +23508,7 @@
       <c r="DS172" s="17"/>
     </row>
     <row r="173" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A173" s="50"/>
+      <c r="A173" s="35"/>
       <c r="B173" s="14"/>
       <c r="C173" s="30">
         <f t="shared" si="2"/>
@@ -23636,7 +23636,7 @@
       <c r="DS173" s="17"/>
     </row>
     <row r="174" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A174" s="50"/>
+      <c r="A174" s="35"/>
       <c r="B174" s="14"/>
       <c r="C174" s="30">
         <f t="shared" si="2"/>
@@ -23764,7 +23764,7 @@
       <c r="DS174" s="17"/>
     </row>
     <row r="175" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A175" s="50"/>
+      <c r="A175" s="35"/>
       <c r="B175" s="14"/>
       <c r="C175" s="30">
         <f t="shared" si="2"/>
@@ -23892,7 +23892,7 @@
       <c r="DS175" s="17"/>
     </row>
     <row r="176" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A176" s="50"/>
+      <c r="A176" s="35"/>
       <c r="B176" s="14"/>
       <c r="C176" s="30">
         <f t="shared" si="2"/>
@@ -24020,7 +24020,7 @@
       <c r="DS176" s="17"/>
     </row>
     <row r="177" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A177" s="50"/>
+      <c r="A177" s="35"/>
       <c r="B177" s="14"/>
       <c r="C177" s="30">
         <f t="shared" si="2"/>
@@ -24148,7 +24148,7 @@
       <c r="DS177" s="17"/>
     </row>
     <row r="178" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A178" s="50"/>
+      <c r="A178" s="35"/>
       <c r="B178" s="14"/>
       <c r="C178" s="30">
         <f t="shared" si="2"/>
@@ -24276,7 +24276,7 @@
       <c r="DS178" s="17"/>
     </row>
     <row r="179" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A179" s="50"/>
+      <c r="A179" s="35"/>
       <c r="B179" s="14"/>
       <c r="C179" s="30">
         <f t="shared" si="2"/>
@@ -24404,7 +24404,7 @@
       <c r="DS179" s="17"/>
     </row>
     <row r="180" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A180" s="50"/>
+      <c r="A180" s="35"/>
       <c r="B180" s="14"/>
       <c r="C180" s="30">
         <f t="shared" si="2"/>
@@ -24532,7 +24532,7 @@
       <c r="DS180" s="17"/>
     </row>
     <row r="181" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A181" s="50"/>
+      <c r="A181" s="35"/>
       <c r="B181" s="14"/>
       <c r="C181" s="30">
         <f t="shared" si="2"/>
@@ -24660,7 +24660,7 @@
       <c r="DS181" s="17"/>
     </row>
     <row r="182" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A182" s="50"/>
+      <c r="A182" s="35"/>
       <c r="B182" s="14"/>
       <c r="C182" s="30">
         <f t="shared" si="2"/>
@@ -24788,7 +24788,7 @@
       <c r="DS182" s="17"/>
     </row>
     <row r="183" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A183" s="50"/>
+      <c r="A183" s="35"/>
       <c r="B183" s="14"/>
       <c r="C183" s="30">
         <f t="shared" si="2"/>
@@ -24916,7 +24916,7 @@
       <c r="DS183" s="17"/>
     </row>
     <row r="184" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A184" s="50"/>
+      <c r="A184" s="35"/>
       <c r="B184" s="14"/>
       <c r="C184" s="30">
         <f t="shared" si="2"/>
@@ -25044,7 +25044,7 @@
       <c r="DS184" s="17"/>
     </row>
     <row r="185" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A185" s="50"/>
+      <c r="A185" s="35"/>
       <c r="B185" s="14"/>
       <c r="C185" s="30">
         <f t="shared" si="2"/>
@@ -25172,7 +25172,7 @@
       <c r="DS185" s="17"/>
     </row>
     <row r="186" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A186" s="50"/>
+      <c r="A186" s="35"/>
       <c r="B186" s="14"/>
       <c r="C186" s="30">
         <f t="shared" si="2"/>
@@ -25300,7 +25300,7 @@
       <c r="DS186" s="17"/>
     </row>
     <row r="187" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A187" s="50"/>
+      <c r="A187" s="35"/>
       <c r="B187" s="14"/>
       <c r="C187" s="30">
         <f t="shared" si="2"/>
@@ -25428,7 +25428,7 @@
       <c r="DS187" s="17"/>
     </row>
     <row r="188" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A188" s="50"/>
+      <c r="A188" s="35"/>
       <c r="B188" s="14"/>
       <c r="C188" s="30">
         <f t="shared" si="2"/>
@@ -25556,7 +25556,7 @@
       <c r="DS188" s="17"/>
     </row>
     <row r="189" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A189" s="50"/>
+      <c r="A189" s="35"/>
       <c r="B189" s="14"/>
       <c r="C189" s="30">
         <f t="shared" si="2"/>
@@ -25684,7 +25684,7 @@
       <c r="DS189" s="17"/>
     </row>
     <row r="190" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A190" s="50"/>
+      <c r="A190" s="35"/>
       <c r="B190" s="14"/>
       <c r="C190" s="30">
         <f t="shared" si="2"/>
@@ -25812,7 +25812,7 @@
       <c r="DS190" s="17"/>
     </row>
     <row r="191" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A191" s="50"/>
+      <c r="A191" s="35"/>
       <c r="B191" s="14"/>
       <c r="C191" s="30">
         <f t="shared" si="2"/>
@@ -25940,7 +25940,7 @@
       <c r="DS191" s="17"/>
     </row>
     <row r="192" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A192" s="50"/>
+      <c r="A192" s="35"/>
       <c r="B192" s="14"/>
       <c r="C192" s="30">
         <f t="shared" si="2"/>
@@ -26068,7 +26068,7 @@
       <c r="DS192" s="17"/>
     </row>
     <row r="193" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A193" s="50"/>
+      <c r="A193" s="35"/>
       <c r="B193" s="14"/>
       <c r="C193" s="30">
         <f t="shared" si="2"/>
@@ -26196,7 +26196,7 @@
       <c r="DS193" s="17"/>
     </row>
     <row r="194" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A194" s="50"/>
+      <c r="A194" s="35"/>
       <c r="B194" s="14"/>
       <c r="C194" s="30">
         <f t="shared" si="2"/>
@@ -26324,7 +26324,7 @@
       <c r="DS194" s="17"/>
     </row>
     <row r="195" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A195" s="50"/>
+      <c r="A195" s="35"/>
       <c r="B195" s="14"/>
       <c r="C195" s="30">
         <f t="shared" si="2"/>
@@ -26452,7 +26452,7 @@
       <c r="DS195" s="17"/>
     </row>
     <row r="196" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A196" s="50"/>
+      <c r="A196" s="35"/>
       <c r="B196" s="14"/>
       <c r="C196" s="30">
         <f t="shared" ref="C196:C259" si="3">SUM(D196:DS196)</f>
@@ -26580,7 +26580,7 @@
       <c r="DS196" s="17"/>
     </row>
     <row r="197" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A197" s="50"/>
+      <c r="A197" s="35"/>
       <c r="B197" s="14"/>
       <c r="C197" s="30">
         <f t="shared" si="3"/>
@@ -26708,7 +26708,7 @@
       <c r="DS197" s="17"/>
     </row>
     <row r="198" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A198" s="50"/>
+      <c r="A198" s="35"/>
       <c r="B198" s="14"/>
       <c r="C198" s="30">
         <f t="shared" si="3"/>
@@ -26836,7 +26836,7 @@
       <c r="DS198" s="17"/>
     </row>
     <row r="199" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A199" s="50"/>
+      <c r="A199" s="35"/>
       <c r="B199" s="14"/>
       <c r="C199" s="30">
         <f t="shared" si="3"/>
@@ -26964,7 +26964,7 @@
       <c r="DS199" s="17"/>
     </row>
     <row r="200" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A200" s="50"/>
+      <c r="A200" s="35"/>
       <c r="B200" s="14"/>
       <c r="C200" s="30">
         <f t="shared" si="3"/>
@@ -27092,7 +27092,7 @@
       <c r="DS200" s="17"/>
     </row>
     <row r="201" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A201" s="50"/>
+      <c r="A201" s="35"/>
       <c r="B201" s="14"/>
       <c r="C201" s="30">
         <f t="shared" si="3"/>
@@ -27220,7 +27220,7 @@
       <c r="DS201" s="17"/>
     </row>
     <row r="202" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A202" s="50"/>
+      <c r="A202" s="35"/>
       <c r="B202" s="14"/>
       <c r="C202" s="30">
         <f t="shared" si="3"/>
@@ -27348,7 +27348,7 @@
       <c r="DS202" s="17"/>
     </row>
     <row r="203" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A203" s="50"/>
+      <c r="A203" s="35"/>
       <c r="B203" s="14"/>
       <c r="C203" s="30">
         <f t="shared" si="3"/>
@@ -27476,7 +27476,7 @@
       <c r="DS203" s="17"/>
     </row>
     <row r="204" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A204" s="50"/>
+      <c r="A204" s="35"/>
       <c r="B204" s="14"/>
       <c r="C204" s="30">
         <f t="shared" si="3"/>
@@ -27604,7 +27604,7 @@
       <c r="DS204" s="17"/>
     </row>
     <row r="205" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A205" s="50"/>
+      <c r="A205" s="35"/>
       <c r="B205" s="14"/>
       <c r="C205" s="30">
         <f t="shared" si="3"/>
@@ -27732,7 +27732,7 @@
       <c r="DS205" s="17"/>
     </row>
     <row r="206" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A206" s="50"/>
+      <c r="A206" s="35"/>
       <c r="B206" s="14"/>
       <c r="C206" s="30">
         <f t="shared" si="3"/>
@@ -27860,7 +27860,7 @@
       <c r="DS206" s="17"/>
     </row>
     <row r="207" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A207" s="50"/>
+      <c r="A207" s="35"/>
       <c r="B207" s="14"/>
       <c r="C207" s="30">
         <f t="shared" si="3"/>
@@ -27988,7 +27988,7 @@
       <c r="DS207" s="17"/>
     </row>
     <row r="208" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A208" s="50"/>
+      <c r="A208" s="35"/>
       <c r="B208" s="14"/>
       <c r="C208" s="30">
         <f t="shared" si="3"/>
@@ -28116,7 +28116,7 @@
       <c r="DS208" s="17"/>
     </row>
     <row r="209" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A209" s="50"/>
+      <c r="A209" s="35"/>
       <c r="B209" s="14"/>
       <c r="C209" s="30">
         <f t="shared" si="3"/>
@@ -28244,7 +28244,7 @@
       <c r="DS209" s="17"/>
     </row>
     <row r="210" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A210" s="50"/>
+      <c r="A210" s="35"/>
       <c r="B210" s="14"/>
       <c r="C210" s="30">
         <f t="shared" si="3"/>
@@ -28372,7 +28372,7 @@
       <c r="DS210" s="17"/>
     </row>
     <row r="211" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A211" s="50"/>
+      <c r="A211" s="35"/>
       <c r="B211" s="14"/>
       <c r="C211" s="30">
         <f t="shared" si="3"/>
@@ -28500,7 +28500,7 @@
       <c r="DS211" s="17"/>
     </row>
     <row r="212" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A212" s="50"/>
+      <c r="A212" s="35"/>
       <c r="B212" s="14"/>
       <c r="C212" s="30">
         <f t="shared" si="3"/>
@@ -28628,7 +28628,7 @@
       <c r="DS212" s="17"/>
     </row>
     <row r="213" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A213" s="50"/>
+      <c r="A213" s="35"/>
       <c r="B213" s="14"/>
       <c r="C213" s="30">
         <f t="shared" si="3"/>
@@ -28756,7 +28756,7 @@
       <c r="DS213" s="17"/>
     </row>
     <row r="214" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A214" s="50"/>
+      <c r="A214" s="35"/>
       <c r="B214" s="14"/>
       <c r="C214" s="30">
         <f t="shared" si="3"/>
@@ -28884,7 +28884,7 @@
       <c r="DS214" s="17"/>
     </row>
     <row r="215" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A215" s="50"/>
+      <c r="A215" s="35"/>
       <c r="B215" s="14"/>
       <c r="C215" s="30">
         <f t="shared" si="3"/>
@@ -29012,7 +29012,7 @@
       <c r="DS215" s="17"/>
     </row>
     <row r="216" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A216" s="50"/>
+      <c r="A216" s="35"/>
       <c r="B216" s="14"/>
       <c r="C216" s="30">
         <f t="shared" si="3"/>
@@ -29140,7 +29140,7 @@
       <c r="DS216" s="17"/>
     </row>
     <row r="217" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A217" s="50"/>
+      <c r="A217" s="35"/>
       <c r="B217" s="14"/>
       <c r="C217" s="30">
         <f t="shared" si="3"/>
@@ -29268,7 +29268,7 @@
       <c r="DS217" s="17"/>
     </row>
     <row r="218" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A218" s="50"/>
+      <c r="A218" s="35"/>
       <c r="B218" s="14"/>
       <c r="C218" s="30">
         <f t="shared" si="3"/>
@@ -29396,7 +29396,7 @@
       <c r="DS218" s="17"/>
     </row>
     <row r="219" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A219" s="50"/>
+      <c r="A219" s="35"/>
       <c r="B219" s="14"/>
       <c r="C219" s="30">
         <f t="shared" si="3"/>
@@ -29524,7 +29524,7 @@
       <c r="DS219" s="17"/>
     </row>
     <row r="220" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A220" s="50"/>
+      <c r="A220" s="35"/>
       <c r="B220" s="14"/>
       <c r="C220" s="30">
         <f t="shared" si="3"/>
@@ -29652,7 +29652,7 @@
       <c r="DS220" s="17"/>
     </row>
     <row r="221" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A221" s="50"/>
+      <c r="A221" s="35"/>
       <c r="B221" s="14"/>
       <c r="C221" s="30">
         <f t="shared" si="3"/>
@@ -29780,7 +29780,7 @@
       <c r="DS221" s="17"/>
     </row>
     <row r="222" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A222" s="50"/>
+      <c r="A222" s="35"/>
       <c r="B222" s="14"/>
       <c r="C222" s="30">
         <f t="shared" si="3"/>
@@ -29908,7 +29908,7 @@
       <c r="DS222" s="17"/>
     </row>
     <row r="223" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A223" s="50"/>
+      <c r="A223" s="35"/>
       <c r="B223" s="14"/>
       <c r="C223" s="30">
         <f t="shared" si="3"/>
@@ -30036,7 +30036,7 @@
       <c r="DS223" s="17"/>
     </row>
     <row r="224" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A224" s="50"/>
+      <c r="A224" s="35"/>
       <c r="B224" s="14"/>
       <c r="C224" s="30">
         <f t="shared" si="3"/>
@@ -30164,7 +30164,7 @@
       <c r="DS224" s="17"/>
     </row>
     <row r="225" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A225" s="50"/>
+      <c r="A225" s="35"/>
       <c r="B225" s="14"/>
       <c r="C225" s="30">
         <f t="shared" si="3"/>
@@ -30292,7 +30292,7 @@
       <c r="DS225" s="17"/>
     </row>
     <row r="226" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A226" s="50"/>
+      <c r="A226" s="35"/>
       <c r="B226" s="14"/>
       <c r="C226" s="30">
         <f t="shared" si="3"/>
@@ -30420,7 +30420,7 @@
       <c r="DS226" s="17"/>
     </row>
     <row r="227" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A227" s="50"/>
+      <c r="A227" s="35"/>
       <c r="B227" s="14"/>
       <c r="C227" s="30">
         <f t="shared" si="3"/>
@@ -30548,7 +30548,7 @@
       <c r="DS227" s="17"/>
     </row>
     <row r="228" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A228" s="50"/>
+      <c r="A228" s="35"/>
       <c r="B228" s="14"/>
       <c r="C228" s="30">
         <f t="shared" si="3"/>
@@ -30676,7 +30676,7 @@
       <c r="DS228" s="17"/>
     </row>
     <row r="229" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A229" s="50"/>
+      <c r="A229" s="35"/>
       <c r="B229" s="14"/>
       <c r="C229" s="30">
         <f t="shared" si="3"/>
@@ -30804,7 +30804,7 @@
       <c r="DS229" s="17"/>
     </row>
     <row r="230" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A230" s="50"/>
+      <c r="A230" s="35"/>
       <c r="B230" s="14"/>
       <c r="C230" s="30">
         <f t="shared" si="3"/>
@@ -30932,7 +30932,7 @@
       <c r="DS230" s="17"/>
     </row>
     <row r="231" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A231" s="50"/>
+      <c r="A231" s="35"/>
       <c r="B231" s="14"/>
       <c r="C231" s="30">
         <f t="shared" si="3"/>
@@ -31060,7 +31060,7 @@
       <c r="DS231" s="17"/>
     </row>
     <row r="232" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A232" s="50"/>
+      <c r="A232" s="35"/>
       <c r="B232" s="14"/>
       <c r="C232" s="30">
         <f t="shared" si="3"/>
@@ -31188,7 +31188,7 @@
       <c r="DS232" s="17"/>
     </row>
     <row r="233" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A233" s="50"/>
+      <c r="A233" s="35"/>
       <c r="B233" s="14"/>
       <c r="C233" s="30">
         <f t="shared" si="3"/>
@@ -31316,7 +31316,7 @@
       <c r="DS233" s="17"/>
     </row>
     <row r="234" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A234" s="50"/>
+      <c r="A234" s="35"/>
       <c r="B234" s="14"/>
       <c r="C234" s="30">
         <f t="shared" si="3"/>
@@ -31444,7 +31444,7 @@
       <c r="DS234" s="17"/>
     </row>
     <row r="235" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A235" s="50"/>
+      <c r="A235" s="35"/>
       <c r="B235" s="14"/>
       <c r="C235" s="30">
         <f t="shared" si="3"/>
@@ -31572,7 +31572,7 @@
       <c r="DS235" s="17"/>
     </row>
     <row r="236" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A236" s="50"/>
+      <c r="A236" s="35"/>
       <c r="B236" s="14"/>
       <c r="C236" s="30">
         <f t="shared" si="3"/>
@@ -31700,7 +31700,7 @@
       <c r="DS236" s="17"/>
     </row>
     <row r="237" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A237" s="50"/>
+      <c r="A237" s="35"/>
       <c r="B237" s="14"/>
       <c r="C237" s="30">
         <f t="shared" si="3"/>
@@ -31828,7 +31828,7 @@
       <c r="DS237" s="17"/>
     </row>
     <row r="238" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A238" s="50"/>
+      <c r="A238" s="35"/>
       <c r="B238" s="14"/>
       <c r="C238" s="30">
         <f t="shared" si="3"/>
@@ -31956,7 +31956,7 @@
       <c r="DS238" s="17"/>
     </row>
     <row r="239" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A239" s="50"/>
+      <c r="A239" s="35"/>
       <c r="B239" s="14"/>
       <c r="C239" s="30">
         <f t="shared" si="3"/>
@@ -32084,7 +32084,7 @@
       <c r="DS239" s="17"/>
     </row>
     <row r="240" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A240" s="50"/>
+      <c r="A240" s="35"/>
       <c r="B240" s="14"/>
       <c r="C240" s="30">
         <f t="shared" si="3"/>
@@ -32212,7 +32212,7 @@
       <c r="DS240" s="17"/>
     </row>
     <row r="241" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A241" s="50"/>
+      <c r="A241" s="35"/>
       <c r="B241" s="14"/>
       <c r="C241" s="30">
         <f t="shared" si="3"/>
@@ -32340,7 +32340,7 @@
       <c r="DS241" s="17"/>
     </row>
     <row r="242" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A242" s="50"/>
+      <c r="A242" s="35"/>
       <c r="B242" s="14"/>
       <c r="C242" s="30">
         <f t="shared" si="3"/>
@@ -32468,7 +32468,7 @@
       <c r="DS242" s="17"/>
     </row>
     <row r="243" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A243" s="50"/>
+      <c r="A243" s="35"/>
       <c r="B243" s="14"/>
       <c r="C243" s="30">
         <f t="shared" si="3"/>
@@ -32596,7 +32596,7 @@
       <c r="DS243" s="17"/>
     </row>
     <row r="244" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A244" s="50"/>
+      <c r="A244" s="35"/>
       <c r="B244" s="14"/>
       <c r="C244" s="30">
         <f t="shared" si="3"/>
@@ -32724,7 +32724,7 @@
       <c r="DS244" s="17"/>
     </row>
     <row r="245" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A245" s="50"/>
+      <c r="A245" s="35"/>
       <c r="B245" s="14"/>
       <c r="C245" s="30">
         <f t="shared" si="3"/>
@@ -32852,7 +32852,7 @@
       <c r="DS245" s="17"/>
     </row>
     <row r="246" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A246" s="50"/>
+      <c r="A246" s="35"/>
       <c r="B246" s="14"/>
       <c r="C246" s="30">
         <f t="shared" si="3"/>
@@ -32980,7 +32980,7 @@
       <c r="DS246" s="17"/>
     </row>
     <row r="247" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A247" s="50"/>
+      <c r="A247" s="35"/>
       <c r="B247" s="14"/>
       <c r="C247" s="30">
         <f t="shared" si="3"/>
@@ -33108,7 +33108,7 @@
       <c r="DS247" s="17"/>
     </row>
     <row r="248" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A248" s="50"/>
+      <c r="A248" s="35"/>
       <c r="B248" s="14"/>
       <c r="C248" s="30">
         <f t="shared" si="3"/>
@@ -33236,7 +33236,7 @@
       <c r="DS248" s="17"/>
     </row>
     <row r="249" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A249" s="50"/>
+      <c r="A249" s="35"/>
       <c r="B249" s="14"/>
       <c r="C249" s="30">
         <f t="shared" si="3"/>
@@ -33364,7 +33364,7 @@
       <c r="DS249" s="17"/>
     </row>
     <row r="250" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A250" s="50"/>
+      <c r="A250" s="35"/>
       <c r="B250" s="14"/>
       <c r="C250" s="30">
         <f t="shared" si="3"/>
@@ -33492,7 +33492,7 @@
       <c r="DS250" s="17"/>
     </row>
     <row r="251" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A251" s="50"/>
+      <c r="A251" s="35"/>
       <c r="B251" s="14"/>
       <c r="C251" s="30">
         <f t="shared" si="3"/>
@@ -33620,7 +33620,7 @@
       <c r="DS251" s="17"/>
     </row>
     <row r="252" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A252" s="50"/>
+      <c r="A252" s="35"/>
       <c r="B252" s="14"/>
       <c r="C252" s="30">
         <f t="shared" si="3"/>
@@ -33748,7 +33748,7 @@
       <c r="DS252" s="17"/>
     </row>
     <row r="253" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A253" s="50"/>
+      <c r="A253" s="35"/>
       <c r="B253" s="14"/>
       <c r="C253" s="30">
         <f t="shared" si="3"/>
@@ -33876,7 +33876,7 @@
       <c r="DS253" s="17"/>
     </row>
     <row r="254" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A254" s="50"/>
+      <c r="A254" s="35"/>
       <c r="B254" s="14"/>
       <c r="C254" s="30">
         <f t="shared" si="3"/>
@@ -34004,7 +34004,7 @@
       <c r="DS254" s="17"/>
     </row>
     <row r="255" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A255" s="50"/>
+      <c r="A255" s="35"/>
       <c r="B255" s="14"/>
       <c r="C255" s="30">
         <f t="shared" si="3"/>
@@ -34132,7 +34132,7 @@
       <c r="DS255" s="17"/>
     </row>
     <row r="256" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A256" s="50"/>
+      <c r="A256" s="35"/>
       <c r="B256" s="14"/>
       <c r="C256" s="30">
         <f t="shared" si="3"/>
@@ -34260,7 +34260,7 @@
       <c r="DS256" s="17"/>
     </row>
     <row r="257" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A257" s="50"/>
+      <c r="A257" s="35"/>
       <c r="B257" s="14"/>
       <c r="C257" s="30">
         <f t="shared" si="3"/>
@@ -34388,7 +34388,7 @@
       <c r="DS257" s="17"/>
     </row>
     <row r="258" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A258" s="50"/>
+      <c r="A258" s="35"/>
       <c r="B258" s="14"/>
       <c r="C258" s="30">
         <f t="shared" si="3"/>
@@ -34516,7 +34516,7 @@
       <c r="DS258" s="17"/>
     </row>
     <row r="259" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A259" s="50"/>
+      <c r="A259" s="35"/>
       <c r="B259" s="14"/>
       <c r="C259" s="30">
         <f t="shared" si="3"/>
@@ -34644,7 +34644,7 @@
       <c r="DS259" s="17"/>
     </row>
     <row r="260" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A260" s="50"/>
+      <c r="A260" s="35"/>
       <c r="B260" s="14"/>
       <c r="C260" s="30">
         <f t="shared" ref="C260:C299" si="4">SUM(D260:DS260)</f>
@@ -34772,7 +34772,7 @@
       <c r="DS260" s="17"/>
     </row>
     <row r="261" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A261" s="50"/>
+      <c r="A261" s="35"/>
       <c r="B261" s="14"/>
       <c r="C261" s="30">
         <f t="shared" si="4"/>
@@ -34900,7 +34900,7 @@
       <c r="DS261" s="17"/>
     </row>
     <row r="262" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A262" s="50"/>
+      <c r="A262" s="35"/>
       <c r="B262" s="14"/>
       <c r="C262" s="30">
         <f t="shared" si="4"/>
@@ -35028,7 +35028,7 @@
       <c r="DS262" s="17"/>
     </row>
     <row r="263" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A263" s="50"/>
+      <c r="A263" s="35"/>
       <c r="B263" s="14"/>
       <c r="C263" s="30">
         <f t="shared" si="4"/>
@@ -35156,7 +35156,7 @@
       <c r="DS263" s="17"/>
     </row>
     <row r="264" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A264" s="50"/>
+      <c r="A264" s="35"/>
       <c r="B264" s="14"/>
       <c r="C264" s="30">
         <f t="shared" si="4"/>
@@ -35284,7 +35284,7 @@
       <c r="DS264" s="17"/>
     </row>
     <row r="265" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A265" s="50"/>
+      <c r="A265" s="35"/>
       <c r="B265" s="14"/>
       <c r="C265" s="30">
         <f t="shared" si="4"/>
@@ -35412,7 +35412,7 @@
       <c r="DS265" s="17"/>
     </row>
     <row r="266" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A266" s="50"/>
+      <c r="A266" s="35"/>
       <c r="B266" s="14"/>
       <c r="C266" s="30">
         <f t="shared" si="4"/>
@@ -35540,7 +35540,7 @@
       <c r="DS266" s="17"/>
     </row>
     <row r="267" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A267" s="50"/>
+      <c r="A267" s="35"/>
       <c r="B267" s="14"/>
       <c r="C267" s="30">
         <f t="shared" si="4"/>
@@ -35668,7 +35668,7 @@
       <c r="DS267" s="17"/>
     </row>
     <row r="268" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A268" s="50"/>
+      <c r="A268" s="35"/>
       <c r="B268" s="14"/>
       <c r="C268" s="30">
         <f t="shared" si="4"/>
@@ -35796,7 +35796,7 @@
       <c r="DS268" s="17"/>
     </row>
     <row r="269" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A269" s="50"/>
+      <c r="A269" s="35"/>
       <c r="B269" s="14"/>
       <c r="C269" s="30">
         <f t="shared" si="4"/>
@@ -35924,7 +35924,7 @@
       <c r="DS269" s="17"/>
     </row>
     <row r="270" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A270" s="50"/>
+      <c r="A270" s="35"/>
       <c r="B270" s="14"/>
       <c r="C270" s="30">
         <f t="shared" si="4"/>
@@ -36052,7 +36052,7 @@
       <c r="DS270" s="17"/>
     </row>
     <row r="271" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A271" s="50"/>
+      <c r="A271" s="35"/>
       <c r="B271" s="14"/>
       <c r="C271" s="30">
         <f t="shared" si="4"/>
@@ -36180,7 +36180,7 @@
       <c r="DS271" s="17"/>
     </row>
     <row r="272" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A272" s="50"/>
+      <c r="A272" s="35"/>
       <c r="B272" s="14"/>
       <c r="C272" s="30">
         <f t="shared" si="4"/>
@@ -36308,7 +36308,7 @@
       <c r="DS272" s="17"/>
     </row>
     <row r="273" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A273" s="50"/>
+      <c r="A273" s="35"/>
       <c r="B273" s="14"/>
       <c r="C273" s="30">
         <f t="shared" si="4"/>
@@ -36436,7 +36436,7 @@
       <c r="DS273" s="17"/>
     </row>
     <row r="274" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A274" s="50"/>
+      <c r="A274" s="35"/>
       <c r="B274" s="14"/>
       <c r="C274" s="30">
         <f t="shared" si="4"/>
@@ -36564,7 +36564,7 @@
       <c r="DS274" s="17"/>
     </row>
     <row r="275" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A275" s="50"/>
+      <c r="A275" s="35"/>
       <c r="B275" s="14"/>
       <c r="C275" s="30">
         <f t="shared" si="4"/>
@@ -36692,7 +36692,7 @@
       <c r="DS275" s="17"/>
     </row>
     <row r="276" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A276" s="50"/>
+      <c r="A276" s="35"/>
       <c r="B276" s="14"/>
       <c r="C276" s="30">
         <f t="shared" si="4"/>
@@ -36820,7 +36820,7 @@
       <c r="DS276" s="17"/>
     </row>
     <row r="277" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A277" s="50"/>
+      <c r="A277" s="35"/>
       <c r="B277" s="14"/>
       <c r="C277" s="30">
         <f t="shared" si="4"/>
@@ -36948,7 +36948,7 @@
       <c r="DS277" s="17"/>
     </row>
     <row r="278" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A278" s="50"/>
+      <c r="A278" s="35"/>
       <c r="B278" s="14"/>
       <c r="C278" s="30">
         <f t="shared" si="4"/>
@@ -37076,7 +37076,7 @@
       <c r="DS278" s="17"/>
     </row>
     <row r="279" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A279" s="50"/>
+      <c r="A279" s="35"/>
       <c r="B279" s="14"/>
       <c r="C279" s="30">
         <f t="shared" si="4"/>
@@ -37204,7 +37204,7 @@
       <c r="DS279" s="17"/>
     </row>
     <row r="280" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A280" s="50"/>
+      <c r="A280" s="35"/>
       <c r="B280" s="14"/>
       <c r="C280" s="30">
         <f t="shared" si="4"/>
@@ -37332,7 +37332,7 @@
       <c r="DS280" s="17"/>
     </row>
     <row r="281" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A281" s="50"/>
+      <c r="A281" s="35"/>
       <c r="B281" s="14"/>
       <c r="C281" s="30">
         <f t="shared" si="4"/>
@@ -37460,7 +37460,7 @@
       <c r="DS281" s="17"/>
     </row>
     <row r="282" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A282" s="50"/>
+      <c r="A282" s="35"/>
       <c r="B282" s="14"/>
       <c r="C282" s="30">
         <f t="shared" si="4"/>
@@ -37588,7 +37588,7 @@
       <c r="DS282" s="17"/>
     </row>
     <row r="283" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A283" s="50"/>
+      <c r="A283" s="35"/>
       <c r="B283" s="14"/>
       <c r="C283" s="30">
         <f t="shared" si="4"/>
@@ -37716,7 +37716,7 @@
       <c r="DS283" s="17"/>
     </row>
     <row r="284" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A284" s="50"/>
+      <c r="A284" s="35"/>
       <c r="B284" s="14"/>
       <c r="C284" s="30">
         <f t="shared" si="4"/>
@@ -37844,7 +37844,7 @@
       <c r="DS284" s="17"/>
     </row>
     <row r="285" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A285" s="50"/>
+      <c r="A285" s="35"/>
       <c r="B285" s="14"/>
       <c r="C285" s="30">
         <f t="shared" si="4"/>
@@ -37972,7 +37972,7 @@
       <c r="DS285" s="17"/>
     </row>
     <row r="286" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A286" s="50"/>
+      <c r="A286" s="35"/>
       <c r="B286" s="14"/>
       <c r="C286" s="30">
         <f t="shared" si="4"/>
@@ -38100,7 +38100,7 @@
       <c r="DS286" s="17"/>
     </row>
     <row r="287" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A287" s="50"/>
+      <c r="A287" s="35"/>
       <c r="B287" s="14"/>
       <c r="C287" s="30">
         <f t="shared" si="4"/>
@@ -38228,7 +38228,7 @@
       <c r="DS287" s="17"/>
     </row>
     <row r="288" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A288" s="50"/>
+      <c r="A288" s="35"/>
       <c r="B288" s="14"/>
       <c r="C288" s="30">
         <f t="shared" si="4"/>
@@ -38356,7 +38356,7 @@
       <c r="DS288" s="17"/>
     </row>
     <row r="289" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A289" s="50"/>
+      <c r="A289" s="35"/>
       <c r="B289" s="14"/>
       <c r="C289" s="30">
         <f t="shared" si="4"/>
@@ -38484,7 +38484,7 @@
       <c r="DS289" s="17"/>
     </row>
     <row r="290" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A290" s="50"/>
+      <c r="A290" s="35"/>
       <c r="B290" s="14"/>
       <c r="C290" s="30">
         <f t="shared" si="4"/>
@@ -38612,7 +38612,7 @@
       <c r="DS290" s="17"/>
     </row>
     <row r="291" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A291" s="50"/>
+      <c r="A291" s="35"/>
       <c r="B291" s="14"/>
       <c r="C291" s="30">
         <f t="shared" si="4"/>
@@ -38740,7 +38740,7 @@
       <c r="DS291" s="17"/>
     </row>
     <row r="292" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A292" s="50"/>
+      <c r="A292" s="35"/>
       <c r="B292" s="14"/>
       <c r="C292" s="30">
         <f t="shared" si="4"/>
@@ -38868,7 +38868,7 @@
       <c r="DS292" s="17"/>
     </row>
     <row r="293" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A293" s="50"/>
+      <c r="A293" s="35"/>
       <c r="B293" s="14"/>
       <c r="C293" s="30">
         <f t="shared" si="4"/>
@@ -38996,7 +38996,7 @@
       <c r="DS293" s="17"/>
     </row>
     <row r="294" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A294" s="50"/>
+      <c r="A294" s="35"/>
       <c r="B294" s="14"/>
       <c r="C294" s="30">
         <f t="shared" si="4"/>
@@ -39124,7 +39124,7 @@
       <c r="DS294" s="17"/>
     </row>
     <row r="295" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A295" s="50"/>
+      <c r="A295" s="35"/>
       <c r="B295" s="14"/>
       <c r="C295" s="30">
         <f t="shared" si="4"/>
@@ -39252,7 +39252,7 @@
       <c r="DS295" s="17"/>
     </row>
     <row r="296" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A296" s="50"/>
+      <c r="A296" s="35"/>
       <c r="B296" s="14"/>
       <c r="C296" s="30">
         <f t="shared" si="4"/>
@@ -39380,7 +39380,7 @@
       <c r="DS296" s="17"/>
     </row>
     <row r="297" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A297" s="50"/>
+      <c r="A297" s="35"/>
       <c r="B297" s="14"/>
       <c r="C297" s="30">
         <f t="shared" si="4"/>
@@ -39508,7 +39508,7 @@
       <c r="DS297" s="17"/>
     </row>
     <row r="298" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A298" s="50"/>
+      <c r="A298" s="35"/>
       <c r="B298" s="14"/>
       <c r="C298" s="30">
         <f t="shared" si="4"/>
@@ -39636,7 +39636,7 @@
       <c r="DS298" s="17"/>
     </row>
     <row r="299" spans="1:123" s="22" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A299" s="51"/>
+      <c r="A299" s="36"/>
       <c r="B299" s="18"/>
       <c r="C299" s="31">
         <f t="shared" si="4"/>
@@ -39768,19 +39768,6 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="AD1:AF1"/>
-    <mergeCell ref="BX2:CA2"/>
-    <mergeCell ref="CJ2:CM2"/>
-    <mergeCell ref="AG1:AK1"/>
-    <mergeCell ref="Z1:AC1"/>
-    <mergeCell ref="BT1:BW1"/>
-    <mergeCell ref="AL1:AO1"/>
-    <mergeCell ref="CV2:CY2"/>
-    <mergeCell ref="AT1:AW1"/>
-    <mergeCell ref="BB1:BG1"/>
-    <mergeCell ref="DH2:DK2"/>
-    <mergeCell ref="BH1:BM1"/>
-    <mergeCell ref="BN1:BS1"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="DP2:DS2"/>
     <mergeCell ref="AX1:BA1"/>
@@ -39797,6 +39784,19 @@
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="N1:Q1"/>
     <mergeCell ref="U1:Y1"/>
+    <mergeCell ref="CV2:CY2"/>
+    <mergeCell ref="AT1:AW1"/>
+    <mergeCell ref="BB1:BG1"/>
+    <mergeCell ref="DH2:DK2"/>
+    <mergeCell ref="BH1:BM1"/>
+    <mergeCell ref="BN1:BS1"/>
+    <mergeCell ref="AD1:AF1"/>
+    <mergeCell ref="BX2:CA2"/>
+    <mergeCell ref="CJ2:CM2"/>
+    <mergeCell ref="AG1:AK1"/>
+    <mergeCell ref="Z1:AC1"/>
+    <mergeCell ref="BT1:BW1"/>
+    <mergeCell ref="AL1:AO1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TEST - SP 2026 - predtekmovanje - rezultati - Copy.xlsx
+++ b/TEST - SP 2026 - predtekmovanje - rezultati - Copy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rihar\Documents\SP2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00630992-A6F5-49B5-B26D-C495FF7CC0D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A46EAE2-0B6B-444B-8A27-ECBC1FD3FF44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-852" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="104">
   <si>
     <t>11.6.</t>
   </si>
@@ -345,27 +345,6 @@
   </si>
   <si>
     <t>L</t>
-  </si>
-  <si>
-    <t>Gregor Bernik</t>
-  </si>
-  <si>
-    <t>Jure Trojar</t>
-  </si>
-  <si>
-    <t>Klemen Zorc</t>
-  </si>
-  <si>
-    <t>Matija Šturm</t>
-  </si>
-  <si>
-    <t>Miralem Delic</t>
-  </si>
-  <si>
-    <t>Ohran Jajcevic</t>
-  </si>
-  <si>
-    <t>Rok Marin</t>
   </si>
 </sst>
 </file>
@@ -920,23 +899,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -956,6 +923,18 @@
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
@@ -1260,108 +1239,108 @@
       <c r="E1" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="39"/>
+      <c r="F1" s="38"/>
       <c r="G1" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="39"/>
+      <c r="H1" s="38"/>
       <c r="I1" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="38"/>
-      <c r="K1" s="38"/>
-      <c r="L1" s="38"/>
-      <c r="M1" s="39"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
+      <c r="L1" s="40"/>
+      <c r="M1" s="38"/>
       <c r="N1" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="O1" s="38"/>
-      <c r="P1" s="38"/>
-      <c r="Q1" s="39"/>
+      <c r="O1" s="40"/>
+      <c r="P1" s="40"/>
+      <c r="Q1" s="38"/>
       <c r="R1" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="S1" s="38"/>
-      <c r="T1" s="39"/>
+      <c r="S1" s="40"/>
+      <c r="T1" s="38"/>
       <c r="U1" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="V1" s="38"/>
-      <c r="W1" s="38"/>
-      <c r="X1" s="38"/>
-      <c r="Y1" s="39"/>
+      <c r="V1" s="40"/>
+      <c r="W1" s="40"/>
+      <c r="X1" s="40"/>
+      <c r="Y1" s="38"/>
       <c r="Z1" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="AA1" s="38"/>
-      <c r="AB1" s="38"/>
-      <c r="AC1" s="39"/>
+      <c r="AA1" s="40"/>
+      <c r="AB1" s="40"/>
+      <c r="AC1" s="38"/>
       <c r="AD1" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="AE1" s="38"/>
-      <c r="AF1" s="39"/>
+      <c r="AE1" s="40"/>
+      <c r="AF1" s="38"/>
       <c r="AG1" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="AH1" s="38"/>
-      <c r="AI1" s="38"/>
-      <c r="AJ1" s="38"/>
-      <c r="AK1" s="39"/>
+      <c r="AH1" s="40"/>
+      <c r="AI1" s="40"/>
+      <c r="AJ1" s="40"/>
+      <c r="AK1" s="38"/>
       <c r="AL1" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="AM1" s="38"/>
-      <c r="AN1" s="38"/>
-      <c r="AO1" s="39"/>
+      <c r="AM1" s="40"/>
+      <c r="AN1" s="40"/>
+      <c r="AO1" s="38"/>
       <c r="AP1" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="AQ1" s="38"/>
-      <c r="AR1" s="38"/>
-      <c r="AS1" s="39"/>
+      <c r="AQ1" s="40"/>
+      <c r="AR1" s="40"/>
+      <c r="AS1" s="38"/>
       <c r="AT1" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="AU1" s="38"/>
-      <c r="AV1" s="38"/>
-      <c r="AW1" s="39"/>
+      <c r="AU1" s="40"/>
+      <c r="AV1" s="40"/>
+      <c r="AW1" s="38"/>
       <c r="AX1" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="AY1" s="38"/>
-      <c r="AZ1" s="38"/>
-      <c r="BA1" s="39"/>
+      <c r="AY1" s="40"/>
+      <c r="AZ1" s="40"/>
+      <c r="BA1" s="38"/>
       <c r="BB1" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="BC1" s="38"/>
-      <c r="BD1" s="38"/>
-      <c r="BE1" s="38"/>
-      <c r="BF1" s="38"/>
-      <c r="BG1" s="39"/>
+      <c r="BC1" s="40"/>
+      <c r="BD1" s="40"/>
+      <c r="BE1" s="40"/>
+      <c r="BF1" s="40"/>
+      <c r="BG1" s="38"/>
       <c r="BH1" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="BI1" s="38"/>
-      <c r="BJ1" s="38"/>
-      <c r="BK1" s="38"/>
-      <c r="BL1" s="38"/>
-      <c r="BM1" s="39"/>
+      <c r="BI1" s="40"/>
+      <c r="BJ1" s="40"/>
+      <c r="BK1" s="40"/>
+      <c r="BL1" s="40"/>
+      <c r="BM1" s="38"/>
       <c r="BN1" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="BO1" s="38"/>
-      <c r="BP1" s="38"/>
-      <c r="BQ1" s="38"/>
-      <c r="BR1" s="38"/>
-      <c r="BS1" s="39"/>
+      <c r="BO1" s="40"/>
+      <c r="BP1" s="40"/>
+      <c r="BQ1" s="40"/>
+      <c r="BR1" s="40"/>
+      <c r="BS1" s="38"/>
       <c r="BT1" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="BU1" s="38"/>
-      <c r="BV1" s="38"/>
-      <c r="BW1" s="39"/>
+      <c r="BU1" s="40"/>
+      <c r="BV1" s="40"/>
+      <c r="BW1" s="38"/>
       <c r="BX1" s="9"/>
     </row>
     <row r="2" spans="1:123" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1590,103 +1569,90 @@
       <c r="BW2" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="BX2" s="40" t="s">
+      <c r="BX2" s="50" t="s">
         <v>93</v>
       </c>
-      <c r="BY2" s="38"/>
-      <c r="BZ2" s="38"/>
-      <c r="CA2" s="39"/>
-      <c r="CB2" s="45" t="s">
+      <c r="BY2" s="40"/>
+      <c r="BZ2" s="40"/>
+      <c r="CA2" s="38"/>
+      <c r="CB2" s="41" t="s">
         <v>94</v>
       </c>
-      <c r="CC2" s="38"/>
-      <c r="CD2" s="38"/>
-      <c r="CE2" s="39"/>
-      <c r="CF2" s="46" t="s">
+      <c r="CC2" s="40"/>
+      <c r="CD2" s="40"/>
+      <c r="CE2" s="38"/>
+      <c r="CF2" s="42" t="s">
         <v>95</v>
       </c>
-      <c r="CG2" s="38"/>
-      <c r="CH2" s="38"/>
-      <c r="CI2" s="39"/>
-      <c r="CJ2" s="41" t="s">
+      <c r="CG2" s="40"/>
+      <c r="CH2" s="40"/>
+      <c r="CI2" s="38"/>
+      <c r="CJ2" s="51" t="s">
         <v>96</v>
       </c>
-      <c r="CK2" s="38"/>
-      <c r="CL2" s="38"/>
-      <c r="CM2" s="39"/>
-      <c r="CN2" s="47" t="s">
+      <c r="CK2" s="40"/>
+      <c r="CL2" s="40"/>
+      <c r="CM2" s="38"/>
+      <c r="CN2" s="43" t="s">
         <v>97</v>
       </c>
-      <c r="CO2" s="38"/>
-      <c r="CP2" s="38"/>
-      <c r="CQ2" s="39"/>
-      <c r="CR2" s="48" t="s">
+      <c r="CO2" s="40"/>
+      <c r="CP2" s="40"/>
+      <c r="CQ2" s="38"/>
+      <c r="CR2" s="44" t="s">
         <v>98</v>
       </c>
-      <c r="CS2" s="38"/>
-      <c r="CT2" s="38"/>
-      <c r="CU2" s="39"/>
-      <c r="CV2" s="42" t="s">
+      <c r="CS2" s="40"/>
+      <c r="CT2" s="40"/>
+      <c r="CU2" s="38"/>
+      <c r="CV2" s="48" t="s">
         <v>99</v>
       </c>
-      <c r="CW2" s="38"/>
-      <c r="CX2" s="38"/>
-      <c r="CY2" s="39"/>
-      <c r="CZ2" s="49" t="s">
+      <c r="CW2" s="40"/>
+      <c r="CX2" s="40"/>
+      <c r="CY2" s="38"/>
+      <c r="CZ2" s="45" t="s">
         <v>100</v>
       </c>
-      <c r="DA2" s="38"/>
-      <c r="DB2" s="38"/>
-      <c r="DC2" s="39"/>
-      <c r="DD2" s="50" t="s">
+      <c r="DA2" s="40"/>
+      <c r="DB2" s="40"/>
+      <c r="DC2" s="38"/>
+      <c r="DD2" s="46" t="s">
         <v>101</v>
       </c>
-      <c r="DE2" s="38"/>
-      <c r="DF2" s="38"/>
-      <c r="DG2" s="39"/>
-      <c r="DH2" s="43" t="s">
+      <c r="DE2" s="40"/>
+      <c r="DF2" s="40"/>
+      <c r="DG2" s="38"/>
+      <c r="DH2" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="DI2" s="38"/>
-      <c r="DJ2" s="38"/>
-      <c r="DK2" s="39"/>
-      <c r="DL2" s="51" t="s">
+      <c r="DI2" s="40"/>
+      <c r="DJ2" s="40"/>
+      <c r="DK2" s="38"/>
+      <c r="DL2" s="47" t="s">
         <v>103</v>
       </c>
-      <c r="DM2" s="38"/>
-      <c r="DN2" s="38"/>
-      <c r="DO2" s="39"/>
-      <c r="DP2" s="44" t="s">
+      <c r="DM2" s="40"/>
+      <c r="DN2" s="40"/>
+      <c r="DO2" s="38"/>
+      <c r="DP2" s="39" t="s">
         <v>95</v>
       </c>
-      <c r="DQ2" s="38"/>
-      <c r="DR2" s="38"/>
-      <c r="DS2" s="39"/>
+      <c r="DQ2" s="40"/>
+      <c r="DR2" s="40"/>
+      <c r="DS2" s="38"/>
     </row>
     <row r="3" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="34"/>
-      <c r="B3" s="10" t="s">
-        <v>104</v>
-      </c>
+      <c r="B3" s="10"/>
       <c r="C3" s="26">
-        <f>SUM(D3:DS3)</f>
-        <v>8</v>
-      </c>
-      <c r="D3" s="27">
-        <v>3</v>
-      </c>
-      <c r="E3" s="11">
-        <v>3</v>
-      </c>
-      <c r="F3" s="13">
-        <v>1</v>
-      </c>
-      <c r="G3" s="11">
         <v>0</v>
       </c>
-      <c r="H3" s="13">
-        <v>1</v>
-      </c>
+      <c r="D3" s="27"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="13"/>
       <c r="I3" s="11"/>
       <c r="J3" s="12"/>
       <c r="K3" s="12"/>
@@ -1805,28 +1771,15 @@
     </row>
     <row r="4" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="35"/>
-      <c r="B4" s="14" t="s">
-        <v>105</v>
-      </c>
+      <c r="B4" s="14"/>
       <c r="C4" s="30">
-        <f t="shared" ref="C4:C67" si="0">SUM(D4:DS4)</f>
-        <v>4</v>
-      </c>
-      <c r="D4" s="28">
-        <v>3</v>
-      </c>
-      <c r="E4" s="15">
         <v>0</v>
       </c>
-      <c r="F4" s="17">
-        <v>0</v>
-      </c>
-      <c r="G4" s="15">
-        <v>0</v>
-      </c>
-      <c r="H4" s="17">
-        <v>1</v>
-      </c>
+      <c r="D4" s="28"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="17"/>
       <c r="I4" s="15"/>
       <c r="J4" s="16"/>
       <c r="K4" s="16"/>
@@ -1945,28 +1898,15 @@
     </row>
     <row r="5" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="35"/>
-      <c r="B5" s="14" t="s">
-        <v>106</v>
-      </c>
+      <c r="B5" s="14"/>
       <c r="C5" s="30">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="D5" s="28">
-        <v>1</v>
-      </c>
-      <c r="E5" s="15">
         <v>0</v>
       </c>
-      <c r="F5" s="17">
-        <v>1</v>
-      </c>
-      <c r="G5" s="15">
-        <v>0</v>
-      </c>
-      <c r="H5" s="17">
-        <v>1</v>
-      </c>
+      <c r="D5" s="28"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="17"/>
       <c r="I5" s="15"/>
       <c r="J5" s="16"/>
       <c r="K5" s="16"/>
@@ -2085,28 +2025,15 @@
     </row>
     <row r="6" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="35"/>
-      <c r="B6" s="14" t="s">
-        <v>107</v>
-      </c>
+      <c r="B6" s="14"/>
       <c r="C6" s="30">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="D6" s="28">
-        <v>1</v>
-      </c>
-      <c r="E6" s="15">
-        <v>3</v>
-      </c>
-      <c r="F6" s="17">
         <v>0</v>
       </c>
-      <c r="G6" s="15">
-        <v>0</v>
-      </c>
-      <c r="H6" s="17">
-        <v>1</v>
-      </c>
+      <c r="D6" s="28"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="17"/>
       <c r="I6" s="15"/>
       <c r="J6" s="16"/>
       <c r="K6" s="16"/>
@@ -2225,28 +2152,15 @@
     </row>
     <row r="7" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="35"/>
-      <c r="B7" s="24" t="s">
-        <v>108</v>
-      </c>
+      <c r="B7" s="24"/>
       <c r="C7" s="30">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="D7" s="28">
-        <v>3</v>
-      </c>
-      <c r="E7" s="15">
         <v>0</v>
       </c>
-      <c r="F7" s="17">
-        <v>0</v>
-      </c>
-      <c r="G7" s="15">
-        <v>0</v>
-      </c>
-      <c r="H7" s="17">
-        <v>3</v>
-      </c>
+      <c r="D7" s="28"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="15"/>
+      <c r="H7" s="17"/>
       <c r="I7" s="15"/>
       <c r="J7" s="16"/>
       <c r="K7" s="16"/>
@@ -2365,28 +2279,15 @@
     </row>
     <row r="8" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="35"/>
-      <c r="B8" s="24" t="s">
-        <v>109</v>
-      </c>
+      <c r="B8" s="24"/>
       <c r="C8" s="30">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="D8" s="28">
-        <v>1</v>
-      </c>
-      <c r="E8" s="15">
         <v>0</v>
       </c>
-      <c r="F8" s="17">
-        <v>0</v>
-      </c>
-      <c r="G8" s="15">
-        <v>0</v>
-      </c>
-      <c r="H8" s="17">
-        <v>1</v>
-      </c>
+      <c r="D8" s="28"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="17"/>
       <c r="I8" s="15"/>
       <c r="J8" s="16"/>
       <c r="K8" s="16"/>
@@ -2505,28 +2406,15 @@
     </row>
     <row r="9" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="35"/>
-      <c r="B9" s="14" t="s">
-        <v>110</v>
-      </c>
+      <c r="B9" s="14"/>
       <c r="C9" s="30">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="D9" s="28">
-        <v>1</v>
-      </c>
-      <c r="E9" s="15">
-        <v>3</v>
-      </c>
-      <c r="F9" s="17">
-        <v>1</v>
-      </c>
-      <c r="G9" s="15">
         <v>0</v>
       </c>
-      <c r="H9" s="17">
-        <v>1</v>
-      </c>
+      <c r="D9" s="28"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="15"/>
+      <c r="H9" s="17"/>
       <c r="I9" s="15"/>
       <c r="J9" s="16"/>
       <c r="K9" s="16"/>
@@ -2647,7 +2535,6 @@
       <c r="A10" s="35"/>
       <c r="B10" s="14"/>
       <c r="C10" s="30">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D10" s="28"/>
@@ -2775,7 +2662,6 @@
       <c r="A11" s="35"/>
       <c r="B11" s="14"/>
       <c r="C11" s="30">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D11" s="28"/>
@@ -2903,7 +2789,6 @@
       <c r="A12" s="35"/>
       <c r="B12" s="14"/>
       <c r="C12" s="30">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D12" s="28"/>
@@ -3031,7 +2916,6 @@
       <c r="A13" s="35"/>
       <c r="B13" s="14"/>
       <c r="C13" s="30">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D13" s="28"/>
@@ -3159,7 +3043,6 @@
       <c r="A14" s="35"/>
       <c r="B14" s="14"/>
       <c r="C14" s="30">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D14" s="28"/>
@@ -3287,7 +3170,6 @@
       <c r="A15" s="35"/>
       <c r="B15" s="14"/>
       <c r="C15" s="30">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D15" s="28"/>
@@ -3415,7 +3297,6 @@
       <c r="A16" s="35"/>
       <c r="B16" s="14"/>
       <c r="C16" s="30">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D16" s="28"/>
@@ -3543,7 +3424,6 @@
       <c r="A17" s="35"/>
       <c r="B17" s="14"/>
       <c r="C17" s="30">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D17" s="28"/>
@@ -3671,7 +3551,6 @@
       <c r="A18" s="35"/>
       <c r="B18" s="14"/>
       <c r="C18" s="30">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D18" s="28"/>
@@ -3799,7 +3678,6 @@
       <c r="A19" s="35"/>
       <c r="B19" s="14"/>
       <c r="C19" s="30">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D19" s="28"/>
@@ -3927,7 +3805,6 @@
       <c r="A20" s="35"/>
       <c r="B20" s="14"/>
       <c r="C20" s="30">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D20" s="28"/>
@@ -4055,7 +3932,6 @@
       <c r="A21" s="35"/>
       <c r="B21" s="14"/>
       <c r="C21" s="30">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D21" s="28"/>
@@ -4183,7 +4059,6 @@
       <c r="A22" s="35"/>
       <c r="B22" s="14"/>
       <c r="C22" s="30">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D22" s="28"/>
@@ -4311,7 +4186,6 @@
       <c r="A23" s="35"/>
       <c r="B23" s="14"/>
       <c r="C23" s="30">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D23" s="28"/>
@@ -4439,7 +4313,6 @@
       <c r="A24" s="35"/>
       <c r="B24" s="14"/>
       <c r="C24" s="30">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D24" s="28"/>
@@ -4567,7 +4440,6 @@
       <c r="A25" s="35"/>
       <c r="B25" s="14"/>
       <c r="C25" s="30">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D25" s="28"/>
@@ -4695,7 +4567,6 @@
       <c r="A26" s="35"/>
       <c r="B26" s="14"/>
       <c r="C26" s="30">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D26" s="28"/>
@@ -4823,7 +4694,6 @@
       <c r="A27" s="35"/>
       <c r="B27" s="14"/>
       <c r="C27" s="30">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D27" s="28"/>
@@ -4951,7 +4821,6 @@
       <c r="A28" s="35"/>
       <c r="B28" s="14"/>
       <c r="C28" s="30">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D28" s="28"/>
@@ -5079,7 +4948,6 @@
       <c r="A29" s="35"/>
       <c r="B29" s="14"/>
       <c r="C29" s="30">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D29" s="28"/>
@@ -5207,7 +5075,6 @@
       <c r="A30" s="35"/>
       <c r="B30" s="14"/>
       <c r="C30" s="30">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D30" s="28"/>
@@ -5335,7 +5202,6 @@
       <c r="A31" s="35"/>
       <c r="B31" s="14"/>
       <c r="C31" s="30">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D31" s="28"/>
@@ -5463,7 +5329,6 @@
       <c r="A32" s="35"/>
       <c r="B32" s="14"/>
       <c r="C32" s="30">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D32" s="28"/>
@@ -5591,7 +5456,6 @@
       <c r="A33" s="35"/>
       <c r="B33" s="14"/>
       <c r="C33" s="30">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D33" s="28"/>
@@ -5719,7 +5583,6 @@
       <c r="A34" s="35"/>
       <c r="B34" s="14"/>
       <c r="C34" s="30">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D34" s="28"/>
@@ -5847,7 +5710,6 @@
       <c r="A35" s="35"/>
       <c r="B35" s="14"/>
       <c r="C35" s="30">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D35" s="28"/>
@@ -5975,7 +5837,6 @@
       <c r="A36" s="35"/>
       <c r="B36" s="14"/>
       <c r="C36" s="30">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D36" s="28"/>
@@ -6103,7 +5964,6 @@
       <c r="A37" s="35"/>
       <c r="B37" s="14"/>
       <c r="C37" s="30">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D37" s="28"/>
@@ -6231,7 +6091,6 @@
       <c r="A38" s="35"/>
       <c r="B38" s="14"/>
       <c r="C38" s="30">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D38" s="28"/>
@@ -6359,7 +6218,6 @@
       <c r="A39" s="35"/>
       <c r="B39" s="14"/>
       <c r="C39" s="30">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D39" s="28"/>
@@ -6487,7 +6345,6 @@
       <c r="A40" s="35"/>
       <c r="B40" s="14"/>
       <c r="C40" s="30">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D40" s="28"/>
@@ -6615,7 +6472,6 @@
       <c r="A41" s="35"/>
       <c r="B41" s="14"/>
       <c r="C41" s="30">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D41" s="28"/>
@@ -6743,7 +6599,6 @@
       <c r="A42" s="35"/>
       <c r="B42" s="14"/>
       <c r="C42" s="30">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D42" s="28"/>
@@ -6871,7 +6726,6 @@
       <c r="A43" s="35"/>
       <c r="B43" s="14"/>
       <c r="C43" s="30">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D43" s="28"/>
@@ -6999,7 +6853,6 @@
       <c r="A44" s="35"/>
       <c r="B44" s="14"/>
       <c r="C44" s="30">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D44" s="28"/>
@@ -7127,7 +6980,6 @@
       <c r="A45" s="35"/>
       <c r="B45" s="14"/>
       <c r="C45" s="30">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D45" s="28"/>
@@ -7255,7 +7107,6 @@
       <c r="A46" s="35"/>
       <c r="B46" s="14"/>
       <c r="C46" s="30">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D46" s="28"/>
@@ -7383,7 +7234,6 @@
       <c r="A47" s="35"/>
       <c r="B47" s="14"/>
       <c r="C47" s="30">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D47" s="28"/>
@@ -7511,7 +7361,6 @@
       <c r="A48" s="35"/>
       <c r="B48" s="14"/>
       <c r="C48" s="30">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D48" s="28"/>
@@ -7639,7 +7488,6 @@
       <c r="A49" s="35"/>
       <c r="B49" s="14"/>
       <c r="C49" s="30">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D49" s="28"/>
@@ -7767,7 +7615,6 @@
       <c r="A50" s="35"/>
       <c r="B50" s="14"/>
       <c r="C50" s="30">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D50" s="28"/>
@@ -7895,7 +7742,6 @@
       <c r="A51" s="35"/>
       <c r="B51" s="14"/>
       <c r="C51" s="30">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D51" s="28"/>
@@ -8023,7 +7869,6 @@
       <c r="A52" s="35"/>
       <c r="B52" s="14"/>
       <c r="C52" s="30">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D52" s="28"/>
@@ -8151,7 +7996,6 @@
       <c r="A53" s="35"/>
       <c r="B53" s="14"/>
       <c r="C53" s="30">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D53" s="28"/>
@@ -8279,7 +8123,6 @@
       <c r="A54" s="35"/>
       <c r="B54" s="14"/>
       <c r="C54" s="30">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D54" s="28"/>
@@ -8407,7 +8250,6 @@
       <c r="A55" s="35"/>
       <c r="B55" s="14"/>
       <c r="C55" s="30">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D55" s="28"/>
@@ -8535,7 +8377,6 @@
       <c r="A56" s="35"/>
       <c r="B56" s="14"/>
       <c r="C56" s="30">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D56" s="28"/>
@@ -8663,7 +8504,6 @@
       <c r="A57" s="35"/>
       <c r="B57" s="14"/>
       <c r="C57" s="30">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D57" s="28"/>
@@ -8791,7 +8631,6 @@
       <c r="A58" s="35"/>
       <c r="B58" s="14"/>
       <c r="C58" s="30">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D58" s="28"/>
@@ -8919,7 +8758,6 @@
       <c r="A59" s="35"/>
       <c r="B59" s="14"/>
       <c r="C59" s="30">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D59" s="28"/>
@@ -9047,7 +8885,6 @@
       <c r="A60" s="35"/>
       <c r="B60" s="14"/>
       <c r="C60" s="30">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D60" s="28"/>
@@ -9175,7 +9012,6 @@
       <c r="A61" s="35"/>
       <c r="B61" s="14"/>
       <c r="C61" s="30">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D61" s="28"/>
@@ -9303,7 +9139,6 @@
       <c r="A62" s="35"/>
       <c r="B62" s="14"/>
       <c r="C62" s="30">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D62" s="28"/>
@@ -9431,7 +9266,6 @@
       <c r="A63" s="35"/>
       <c r="B63" s="14"/>
       <c r="C63" s="30">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D63" s="28"/>
@@ -9559,7 +9393,6 @@
       <c r="A64" s="35"/>
       <c r="B64" s="14"/>
       <c r="C64" s="30">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D64" s="28"/>
@@ -9687,7 +9520,6 @@
       <c r="A65" s="35"/>
       <c r="B65" s="14"/>
       <c r="C65" s="30">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D65" s="28"/>
@@ -9815,7 +9647,6 @@
       <c r="A66" s="35"/>
       <c r="B66" s="14"/>
       <c r="C66" s="30">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D66" s="28"/>
@@ -9943,7 +9774,6 @@
       <c r="A67" s="35"/>
       <c r="B67" s="14"/>
       <c r="C67" s="30">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D67" s="28"/>
@@ -10071,7 +9901,6 @@
       <c r="A68" s="35"/>
       <c r="B68" s="14"/>
       <c r="C68" s="30">
-        <f t="shared" ref="C68:C131" si="1">SUM(D68:DS68)</f>
         <v>0</v>
       </c>
       <c r="D68" s="28"/>
@@ -10199,7 +10028,6 @@
       <c r="A69" s="35"/>
       <c r="B69" s="14"/>
       <c r="C69" s="30">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D69" s="28"/>
@@ -10327,7 +10155,6 @@
       <c r="A70" s="35"/>
       <c r="B70" s="14"/>
       <c r="C70" s="30">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D70" s="28"/>
@@ -10455,7 +10282,6 @@
       <c r="A71" s="35"/>
       <c r="B71" s="14"/>
       <c r="C71" s="30">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D71" s="28"/>
@@ -10583,7 +10409,6 @@
       <c r="A72" s="35"/>
       <c r="B72" s="14"/>
       <c r="C72" s="30">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D72" s="28"/>
@@ -10711,7 +10536,6 @@
       <c r="A73" s="35"/>
       <c r="B73" s="14"/>
       <c r="C73" s="30">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D73" s="28"/>
@@ -10839,7 +10663,6 @@
       <c r="A74" s="35"/>
       <c r="B74" s="14"/>
       <c r="C74" s="30">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D74" s="28"/>
@@ -10967,7 +10790,6 @@
       <c r="A75" s="35"/>
       <c r="B75" s="14"/>
       <c r="C75" s="30">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D75" s="28"/>
@@ -11095,7 +10917,6 @@
       <c r="A76" s="35"/>
       <c r="B76" s="14"/>
       <c r="C76" s="30">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D76" s="28"/>
@@ -11223,7 +11044,6 @@
       <c r="A77" s="35"/>
       <c r="B77" s="14"/>
       <c r="C77" s="30">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D77" s="28"/>
@@ -11351,7 +11171,6 @@
       <c r="A78" s="35"/>
       <c r="B78" s="14"/>
       <c r="C78" s="30">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D78" s="28"/>
@@ -11479,7 +11298,6 @@
       <c r="A79" s="35"/>
       <c r="B79" s="14"/>
       <c r="C79" s="30">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D79" s="28"/>
@@ -11607,7 +11425,6 @@
       <c r="A80" s="35"/>
       <c r="B80" s="14"/>
       <c r="C80" s="30">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D80" s="28"/>
@@ -11735,7 +11552,6 @@
       <c r="A81" s="35"/>
       <c r="B81" s="14"/>
       <c r="C81" s="30">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D81" s="28"/>
@@ -11863,7 +11679,6 @@
       <c r="A82" s="35"/>
       <c r="B82" s="14"/>
       <c r="C82" s="30">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D82" s="28"/>
@@ -11991,7 +11806,6 @@
       <c r="A83" s="35"/>
       <c r="B83" s="14"/>
       <c r="C83" s="30">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D83" s="28"/>
@@ -12119,7 +11933,6 @@
       <c r="A84" s="35"/>
       <c r="B84" s="14"/>
       <c r="C84" s="30">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D84" s="28"/>
@@ -12247,7 +12060,6 @@
       <c r="A85" s="35"/>
       <c r="B85" s="14"/>
       <c r="C85" s="30">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D85" s="28"/>
@@ -12375,7 +12187,6 @@
       <c r="A86" s="35"/>
       <c r="B86" s="14"/>
       <c r="C86" s="30">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D86" s="28"/>
@@ -12503,7 +12314,6 @@
       <c r="A87" s="35"/>
       <c r="B87" s="14"/>
       <c r="C87" s="30">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D87" s="28"/>
@@ -12631,7 +12441,6 @@
       <c r="A88" s="35"/>
       <c r="B88" s="14"/>
       <c r="C88" s="30">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D88" s="28"/>
@@ -12759,7 +12568,6 @@
       <c r="A89" s="35"/>
       <c r="B89" s="14"/>
       <c r="C89" s="30">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D89" s="28"/>
@@ -12887,7 +12695,6 @@
       <c r="A90" s="35"/>
       <c r="B90" s="14"/>
       <c r="C90" s="30">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D90" s="28"/>
@@ -13015,7 +12822,6 @@
       <c r="A91" s="35"/>
       <c r="B91" s="14"/>
       <c r="C91" s="30">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D91" s="28"/>
@@ -13143,7 +12949,6 @@
       <c r="A92" s="35"/>
       <c r="B92" s="14"/>
       <c r="C92" s="30">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D92" s="28"/>
@@ -13271,7 +13076,6 @@
       <c r="A93" s="35"/>
       <c r="B93" s="14"/>
       <c r="C93" s="30">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D93" s="28"/>
@@ -13399,7 +13203,6 @@
       <c r="A94" s="35"/>
       <c r="B94" s="14"/>
       <c r="C94" s="30">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D94" s="28"/>
@@ -13527,7 +13330,6 @@
       <c r="A95" s="35"/>
       <c r="B95" s="14"/>
       <c r="C95" s="30">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D95" s="28"/>
@@ -13655,7 +13457,6 @@
       <c r="A96" s="35"/>
       <c r="B96" s="14"/>
       <c r="C96" s="30">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D96" s="28"/>
@@ -13783,7 +13584,6 @@
       <c r="A97" s="35"/>
       <c r="B97" s="14"/>
       <c r="C97" s="30">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D97" s="28"/>
@@ -13911,7 +13711,6 @@
       <c r="A98" s="35"/>
       <c r="B98" s="14"/>
       <c r="C98" s="30">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D98" s="28"/>
@@ -14039,7 +13838,6 @@
       <c r="A99" s="35"/>
       <c r="B99" s="14"/>
       <c r="C99" s="30">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D99" s="28"/>
@@ -14167,7 +13965,6 @@
       <c r="A100" s="35"/>
       <c r="B100" s="14"/>
       <c r="C100" s="30">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D100" s="28"/>
@@ -14295,7 +14092,6 @@
       <c r="A101" s="35"/>
       <c r="B101" s="14"/>
       <c r="C101" s="30">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D101" s="28"/>
@@ -14423,7 +14219,6 @@
       <c r="A102" s="35"/>
       <c r="B102" s="14"/>
       <c r="C102" s="30">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D102" s="28"/>
@@ -14551,7 +14346,6 @@
       <c r="A103" s="35"/>
       <c r="B103" s="14"/>
       <c r="C103" s="30">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D103" s="28"/>
@@ -14679,7 +14473,6 @@
       <c r="A104" s="35"/>
       <c r="B104" s="14"/>
       <c r="C104" s="30">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D104" s="28"/>
@@ -14807,7 +14600,6 @@
       <c r="A105" s="35"/>
       <c r="B105" s="14"/>
       <c r="C105" s="30">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D105" s="28"/>
@@ -14935,7 +14727,6 @@
       <c r="A106" s="35"/>
       <c r="B106" s="14"/>
       <c r="C106" s="30">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D106" s="28"/>
@@ -15063,7 +14854,6 @@
       <c r="A107" s="35"/>
       <c r="B107" s="14"/>
       <c r="C107" s="30">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D107" s="28"/>
@@ -15191,7 +14981,6 @@
       <c r="A108" s="35"/>
       <c r="B108" s="14"/>
       <c r="C108" s="30">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D108" s="28"/>
@@ -15319,7 +15108,6 @@
       <c r="A109" s="35"/>
       <c r="B109" s="14"/>
       <c r="C109" s="30">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D109" s="28"/>
@@ -15447,7 +15235,6 @@
       <c r="A110" s="35"/>
       <c r="B110" s="14"/>
       <c r="C110" s="30">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D110" s="28"/>
@@ -15575,7 +15362,6 @@
       <c r="A111" s="35"/>
       <c r="B111" s="14"/>
       <c r="C111" s="30">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D111" s="28"/>
@@ -15703,7 +15489,6 @@
       <c r="A112" s="35"/>
       <c r="B112" s="14"/>
       <c r="C112" s="30">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D112" s="28"/>
@@ -15831,7 +15616,6 @@
       <c r="A113" s="35"/>
       <c r="B113" s="14"/>
       <c r="C113" s="30">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D113" s="28"/>
@@ -15959,7 +15743,6 @@
       <c r="A114" s="35"/>
       <c r="B114" s="14"/>
       <c r="C114" s="30">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D114" s="28"/>
@@ -16087,7 +15870,6 @@
       <c r="A115" s="35"/>
       <c r="B115" s="14"/>
       <c r="C115" s="30">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D115" s="28"/>
@@ -16215,7 +15997,6 @@
       <c r="A116" s="35"/>
       <c r="B116" s="14"/>
       <c r="C116" s="30">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D116" s="28"/>
@@ -16343,7 +16124,6 @@
       <c r="A117" s="35"/>
       <c r="B117" s="14"/>
       <c r="C117" s="30">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D117" s="28"/>
@@ -16471,7 +16251,6 @@
       <c r="A118" s="35"/>
       <c r="B118" s="14"/>
       <c r="C118" s="30">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D118" s="28"/>
@@ -16599,7 +16378,6 @@
       <c r="A119" s="35"/>
       <c r="B119" s="14"/>
       <c r="C119" s="30">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D119" s="28"/>
@@ -16727,7 +16505,6 @@
       <c r="A120" s="35"/>
       <c r="B120" s="14"/>
       <c r="C120" s="30">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D120" s="28"/>
@@ -16855,7 +16632,6 @@
       <c r="A121" s="35"/>
       <c r="B121" s="14"/>
       <c r="C121" s="30">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D121" s="28"/>
@@ -16983,7 +16759,6 @@
       <c r="A122" s="35"/>
       <c r="B122" s="14"/>
       <c r="C122" s="30">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D122" s="28"/>
@@ -17111,7 +16886,6 @@
       <c r="A123" s="35"/>
       <c r="B123" s="14"/>
       <c r="C123" s="30">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D123" s="28"/>
@@ -17239,7 +17013,6 @@
       <c r="A124" s="35"/>
       <c r="B124" s="14"/>
       <c r="C124" s="30">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D124" s="28"/>
@@ -17367,7 +17140,6 @@
       <c r="A125" s="35"/>
       <c r="B125" s="14"/>
       <c r="C125" s="30">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D125" s="28"/>
@@ -17495,7 +17267,6 @@
       <c r="A126" s="35"/>
       <c r="B126" s="14"/>
       <c r="C126" s="30">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D126" s="28"/>
@@ -17623,7 +17394,6 @@
       <c r="A127" s="35"/>
       <c r="B127" s="14"/>
       <c r="C127" s="30">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D127" s="28"/>
@@ -17751,7 +17521,6 @@
       <c r="A128" s="35"/>
       <c r="B128" s="14"/>
       <c r="C128" s="30">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D128" s="28"/>
@@ -17879,7 +17648,6 @@
       <c r="A129" s="35"/>
       <c r="B129" s="14"/>
       <c r="C129" s="30">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D129" s="28"/>
@@ -18007,7 +17775,6 @@
       <c r="A130" s="35"/>
       <c r="B130" s="14"/>
       <c r="C130" s="30">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D130" s="28"/>
@@ -18135,7 +17902,6 @@
       <c r="A131" s="35"/>
       <c r="B131" s="14"/>
       <c r="C131" s="30">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D131" s="28"/>
@@ -18263,7 +18029,6 @@
       <c r="A132" s="35"/>
       <c r="B132" s="14"/>
       <c r="C132" s="30">
-        <f t="shared" ref="C132:C195" si="2">SUM(D132:DS132)</f>
         <v>0</v>
       </c>
       <c r="D132" s="28"/>
@@ -18391,7 +18156,6 @@
       <c r="A133" s="35"/>
       <c r="B133" s="14"/>
       <c r="C133" s="30">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D133" s="28"/>
@@ -18519,7 +18283,6 @@
       <c r="A134" s="35"/>
       <c r="B134" s="14"/>
       <c r="C134" s="30">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D134" s="28"/>
@@ -18647,7 +18410,6 @@
       <c r="A135" s="35"/>
       <c r="B135" s="14"/>
       <c r="C135" s="30">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D135" s="28"/>
@@ -18775,7 +18537,6 @@
       <c r="A136" s="35"/>
       <c r="B136" s="14"/>
       <c r="C136" s="30">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D136" s="28"/>
@@ -18903,7 +18664,6 @@
       <c r="A137" s="35"/>
       <c r="B137" s="14"/>
       <c r="C137" s="30">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D137" s="28"/>
@@ -19031,7 +18791,6 @@
       <c r="A138" s="35"/>
       <c r="B138" s="14"/>
       <c r="C138" s="30">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D138" s="28"/>
@@ -19159,7 +18918,6 @@
       <c r="A139" s="35"/>
       <c r="B139" s="14"/>
       <c r="C139" s="30">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D139" s="28"/>
@@ -19287,7 +19045,6 @@
       <c r="A140" s="35"/>
       <c r="B140" s="14"/>
       <c r="C140" s="30">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D140" s="28"/>
@@ -19415,7 +19172,6 @@
       <c r="A141" s="35"/>
       <c r="B141" s="14"/>
       <c r="C141" s="30">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D141" s="28"/>
@@ -19543,7 +19299,6 @@
       <c r="A142" s="35"/>
       <c r="B142" s="14"/>
       <c r="C142" s="30">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D142" s="28"/>
@@ -19671,7 +19426,6 @@
       <c r="A143" s="35"/>
       <c r="B143" s="14"/>
       <c r="C143" s="30">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D143" s="28"/>
@@ -19799,7 +19553,6 @@
       <c r="A144" s="35"/>
       <c r="B144" s="14"/>
       <c r="C144" s="30">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D144" s="28"/>
@@ -19927,7 +19680,6 @@
       <c r="A145" s="35"/>
       <c r="B145" s="14"/>
       <c r="C145" s="30">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D145" s="28"/>
@@ -20055,7 +19807,6 @@
       <c r="A146" s="35"/>
       <c r="B146" s="14"/>
       <c r="C146" s="30">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D146" s="28"/>
@@ -20183,7 +19934,6 @@
       <c r="A147" s="35"/>
       <c r="B147" s="14"/>
       <c r="C147" s="30">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D147" s="28"/>
@@ -20311,7 +20061,6 @@
       <c r="A148" s="35"/>
       <c r="B148" s="14"/>
       <c r="C148" s="30">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D148" s="28"/>
@@ -20439,7 +20188,6 @@
       <c r="A149" s="35"/>
       <c r="B149" s="14"/>
       <c r="C149" s="30">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D149" s="28"/>
@@ -20567,7 +20315,6 @@
       <c r="A150" s="35"/>
       <c r="B150" s="14"/>
       <c r="C150" s="30">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D150" s="28"/>
@@ -20695,7 +20442,6 @@
       <c r="A151" s="35"/>
       <c r="B151" s="14"/>
       <c r="C151" s="30">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D151" s="28"/>
@@ -20823,7 +20569,6 @@
       <c r="A152" s="35"/>
       <c r="B152" s="14"/>
       <c r="C152" s="30">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D152" s="28"/>
@@ -20951,7 +20696,6 @@
       <c r="A153" s="35"/>
       <c r="B153" s="14"/>
       <c r="C153" s="30">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D153" s="28"/>
@@ -21079,7 +20823,6 @@
       <c r="A154" s="35"/>
       <c r="B154" s="14"/>
       <c r="C154" s="30">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D154" s="28"/>
@@ -21207,7 +20950,6 @@
       <c r="A155" s="35"/>
       <c r="B155" s="14"/>
       <c r="C155" s="30">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D155" s="28"/>
@@ -21335,7 +21077,6 @@
       <c r="A156" s="35"/>
       <c r="B156" s="14"/>
       <c r="C156" s="30">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D156" s="28"/>
@@ -21463,7 +21204,6 @@
       <c r="A157" s="35"/>
       <c r="B157" s="14"/>
       <c r="C157" s="30">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D157" s="28"/>
@@ -21591,7 +21331,6 @@
       <c r="A158" s="35"/>
       <c r="B158" s="14"/>
       <c r="C158" s="30">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D158" s="28"/>
@@ -21719,7 +21458,6 @@
       <c r="A159" s="35"/>
       <c r="B159" s="14"/>
       <c r="C159" s="30">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D159" s="28"/>
@@ -21847,7 +21585,6 @@
       <c r="A160" s="35"/>
       <c r="B160" s="14"/>
       <c r="C160" s="30">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D160" s="28"/>
@@ -21975,7 +21712,6 @@
       <c r="A161" s="35"/>
       <c r="B161" s="14"/>
       <c r="C161" s="30">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D161" s="28"/>
@@ -22103,7 +21839,6 @@
       <c r="A162" s="35"/>
       <c r="B162" s="14"/>
       <c r="C162" s="30">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D162" s="28"/>
@@ -22231,7 +21966,6 @@
       <c r="A163" s="35"/>
       <c r="B163" s="14"/>
       <c r="C163" s="30">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D163" s="28"/>
@@ -22359,7 +22093,6 @@
       <c r="A164" s="35"/>
       <c r="B164" s="14"/>
       <c r="C164" s="30">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D164" s="28"/>
@@ -22487,7 +22220,6 @@
       <c r="A165" s="35"/>
       <c r="B165" s="14"/>
       <c r="C165" s="30">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D165" s="28"/>
@@ -22615,7 +22347,6 @@
       <c r="A166" s="35"/>
       <c r="B166" s="14"/>
       <c r="C166" s="30">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D166" s="28"/>
@@ -22743,7 +22474,6 @@
       <c r="A167" s="35"/>
       <c r="B167" s="14"/>
       <c r="C167" s="30">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D167" s="28"/>
@@ -22871,7 +22601,6 @@
       <c r="A168" s="35"/>
       <c r="B168" s="14"/>
       <c r="C168" s="30">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D168" s="28"/>
@@ -22999,7 +22728,6 @@
       <c r="A169" s="35"/>
       <c r="B169" s="14"/>
       <c r="C169" s="30">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D169" s="28"/>
@@ -23127,7 +22855,6 @@
       <c r="A170" s="35"/>
       <c r="B170" s="14"/>
       <c r="C170" s="30">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D170" s="28"/>
@@ -23255,7 +22982,6 @@
       <c r="A171" s="35"/>
       <c r="B171" s="14"/>
       <c r="C171" s="30">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D171" s="28"/>
@@ -23383,7 +23109,6 @@
       <c r="A172" s="35"/>
       <c r="B172" s="14"/>
       <c r="C172" s="30">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D172" s="28"/>
@@ -23511,7 +23236,6 @@
       <c r="A173" s="35"/>
       <c r="B173" s="14"/>
       <c r="C173" s="30">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D173" s="28"/>
@@ -23639,7 +23363,6 @@
       <c r="A174" s="35"/>
       <c r="B174" s="14"/>
       <c r="C174" s="30">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D174" s="28"/>
@@ -23767,7 +23490,6 @@
       <c r="A175" s="35"/>
       <c r="B175" s="14"/>
       <c r="C175" s="30">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D175" s="28"/>
@@ -23895,7 +23617,6 @@
       <c r="A176" s="35"/>
       <c r="B176" s="14"/>
       <c r="C176" s="30">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D176" s="28"/>
@@ -24023,7 +23744,6 @@
       <c r="A177" s="35"/>
       <c r="B177" s="14"/>
       <c r="C177" s="30">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D177" s="28"/>
@@ -24151,7 +23871,6 @@
       <c r="A178" s="35"/>
       <c r="B178" s="14"/>
       <c r="C178" s="30">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D178" s="28"/>
@@ -24279,7 +23998,6 @@
       <c r="A179" s="35"/>
       <c r="B179" s="14"/>
       <c r="C179" s="30">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D179" s="28"/>
@@ -24407,7 +24125,6 @@
       <c r="A180" s="35"/>
       <c r="B180" s="14"/>
       <c r="C180" s="30">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D180" s="28"/>
@@ -24535,7 +24252,6 @@
       <c r="A181" s="35"/>
       <c r="B181" s="14"/>
       <c r="C181" s="30">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D181" s="28"/>
@@ -24663,7 +24379,6 @@
       <c r="A182" s="35"/>
       <c r="B182" s="14"/>
       <c r="C182" s="30">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D182" s="28"/>
@@ -24791,7 +24506,6 @@
       <c r="A183" s="35"/>
       <c r="B183" s="14"/>
       <c r="C183" s="30">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D183" s="28"/>
@@ -24919,7 +24633,6 @@
       <c r="A184" s="35"/>
       <c r="B184" s="14"/>
       <c r="C184" s="30">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D184" s="28"/>
@@ -25047,7 +24760,6 @@
       <c r="A185" s="35"/>
       <c r="B185" s="14"/>
       <c r="C185" s="30">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D185" s="28"/>
@@ -25175,7 +24887,6 @@
       <c r="A186" s="35"/>
       <c r="B186" s="14"/>
       <c r="C186" s="30">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D186" s="28"/>
@@ -25303,7 +25014,6 @@
       <c r="A187" s="35"/>
       <c r="B187" s="14"/>
       <c r="C187" s="30">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D187" s="28"/>
@@ -25431,7 +25141,6 @@
       <c r="A188" s="35"/>
       <c r="B188" s="14"/>
       <c r="C188" s="30">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D188" s="28"/>
@@ -25559,7 +25268,6 @@
       <c r="A189" s="35"/>
       <c r="B189" s="14"/>
       <c r="C189" s="30">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D189" s="28"/>
@@ -25687,7 +25395,6 @@
       <c r="A190" s="35"/>
       <c r="B190" s="14"/>
       <c r="C190" s="30">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D190" s="28"/>
@@ -25815,7 +25522,6 @@
       <c r="A191" s="35"/>
       <c r="B191" s="14"/>
       <c r="C191" s="30">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D191" s="28"/>
@@ -25943,7 +25649,6 @@
       <c r="A192" s="35"/>
       <c r="B192" s="14"/>
       <c r="C192" s="30">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D192" s="28"/>
@@ -26071,7 +25776,6 @@
       <c r="A193" s="35"/>
       <c r="B193" s="14"/>
       <c r="C193" s="30">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D193" s="28"/>
@@ -26199,7 +25903,6 @@
       <c r="A194" s="35"/>
       <c r="B194" s="14"/>
       <c r="C194" s="30">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D194" s="28"/>
@@ -26327,7 +26030,6 @@
       <c r="A195" s="35"/>
       <c r="B195" s="14"/>
       <c r="C195" s="30">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D195" s="28"/>
@@ -26455,7 +26157,6 @@
       <c r="A196" s="35"/>
       <c r="B196" s="14"/>
       <c r="C196" s="30">
-        <f t="shared" ref="C196:C259" si="3">SUM(D196:DS196)</f>
         <v>0</v>
       </c>
       <c r="D196" s="28"/>
@@ -26583,7 +26284,6 @@
       <c r="A197" s="35"/>
       <c r="B197" s="14"/>
       <c r="C197" s="30">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D197" s="28"/>
@@ -26711,7 +26411,6 @@
       <c r="A198" s="35"/>
       <c r="B198" s="14"/>
       <c r="C198" s="30">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D198" s="28"/>
@@ -26839,7 +26538,6 @@
       <c r="A199" s="35"/>
       <c r="B199" s="14"/>
       <c r="C199" s="30">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D199" s="28"/>
@@ -26967,7 +26665,6 @@
       <c r="A200" s="35"/>
       <c r="B200" s="14"/>
       <c r="C200" s="30">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D200" s="28"/>
@@ -27095,7 +26792,6 @@
       <c r="A201" s="35"/>
       <c r="B201" s="14"/>
       <c r="C201" s="30">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D201" s="28"/>
@@ -27223,7 +26919,6 @@
       <c r="A202" s="35"/>
       <c r="B202" s="14"/>
       <c r="C202" s="30">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D202" s="28"/>
@@ -27351,7 +27046,6 @@
       <c r="A203" s="35"/>
       <c r="B203" s="14"/>
       <c r="C203" s="30">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D203" s="28"/>
@@ -27479,7 +27173,6 @@
       <c r="A204" s="35"/>
       <c r="B204" s="14"/>
       <c r="C204" s="30">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D204" s="28"/>
@@ -27607,7 +27300,6 @@
       <c r="A205" s="35"/>
       <c r="B205" s="14"/>
       <c r="C205" s="30">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D205" s="28"/>
@@ -27735,7 +27427,6 @@
       <c r="A206" s="35"/>
       <c r="B206" s="14"/>
       <c r="C206" s="30">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D206" s="28"/>
@@ -27863,7 +27554,6 @@
       <c r="A207" s="35"/>
       <c r="B207" s="14"/>
       <c r="C207" s="30">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D207" s="28"/>
@@ -27991,7 +27681,6 @@
       <c r="A208" s="35"/>
       <c r="B208" s="14"/>
       <c r="C208" s="30">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D208" s="28"/>
@@ -28119,7 +27808,6 @@
       <c r="A209" s="35"/>
       <c r="B209" s="14"/>
       <c r="C209" s="30">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D209" s="28"/>
@@ -28247,7 +27935,6 @@
       <c r="A210" s="35"/>
       <c r="B210" s="14"/>
       <c r="C210" s="30">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D210" s="28"/>
@@ -28375,7 +28062,6 @@
       <c r="A211" s="35"/>
       <c r="B211" s="14"/>
       <c r="C211" s="30">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D211" s="28"/>
@@ -28503,7 +28189,6 @@
       <c r="A212" s="35"/>
       <c r="B212" s="14"/>
       <c r="C212" s="30">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D212" s="28"/>
@@ -28631,7 +28316,6 @@
       <c r="A213" s="35"/>
       <c r="B213" s="14"/>
       <c r="C213" s="30">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D213" s="28"/>
@@ -28759,7 +28443,6 @@
       <c r="A214" s="35"/>
       <c r="B214" s="14"/>
       <c r="C214" s="30">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D214" s="28"/>
@@ -28887,7 +28570,6 @@
       <c r="A215" s="35"/>
       <c r="B215" s="14"/>
       <c r="C215" s="30">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D215" s="28"/>
@@ -29015,7 +28697,6 @@
       <c r="A216" s="35"/>
       <c r="B216" s="14"/>
       <c r="C216" s="30">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D216" s="28"/>
@@ -29143,7 +28824,6 @@
       <c r="A217" s="35"/>
       <c r="B217" s="14"/>
       <c r="C217" s="30">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D217" s="28"/>
@@ -29271,7 +28951,6 @@
       <c r="A218" s="35"/>
       <c r="B218" s="14"/>
       <c r="C218" s="30">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D218" s="28"/>
@@ -29399,7 +29078,6 @@
       <c r="A219" s="35"/>
       <c r="B219" s="14"/>
       <c r="C219" s="30">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D219" s="28"/>
@@ -29527,7 +29205,6 @@
       <c r="A220" s="35"/>
       <c r="B220" s="14"/>
       <c r="C220" s="30">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D220" s="28"/>
@@ -29655,7 +29332,6 @@
       <c r="A221" s="35"/>
       <c r="B221" s="14"/>
       <c r="C221" s="30">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D221" s="28"/>
@@ -29783,7 +29459,6 @@
       <c r="A222" s="35"/>
       <c r="B222" s="14"/>
       <c r="C222" s="30">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D222" s="28"/>
@@ -29911,7 +29586,6 @@
       <c r="A223" s="35"/>
       <c r="B223" s="14"/>
       <c r="C223" s="30">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D223" s="28"/>
@@ -30039,7 +29713,6 @@
       <c r="A224" s="35"/>
       <c r="B224" s="14"/>
       <c r="C224" s="30">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D224" s="28"/>
@@ -30167,7 +29840,6 @@
       <c r="A225" s="35"/>
       <c r="B225" s="14"/>
       <c r="C225" s="30">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D225" s="28"/>
@@ -30295,7 +29967,6 @@
       <c r="A226" s="35"/>
       <c r="B226" s="14"/>
       <c r="C226" s="30">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D226" s="28"/>
@@ -30423,7 +30094,6 @@
       <c r="A227" s="35"/>
       <c r="B227" s="14"/>
       <c r="C227" s="30">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D227" s="28"/>
@@ -30551,7 +30221,6 @@
       <c r="A228" s="35"/>
       <c r="B228" s="14"/>
       <c r="C228" s="30">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D228" s="28"/>
@@ -30679,7 +30348,6 @@
       <c r="A229" s="35"/>
       <c r="B229" s="14"/>
       <c r="C229" s="30">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D229" s="28"/>
@@ -30807,7 +30475,6 @@
       <c r="A230" s="35"/>
       <c r="B230" s="14"/>
       <c r="C230" s="30">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D230" s="28"/>
@@ -30935,7 +30602,6 @@
       <c r="A231" s="35"/>
       <c r="B231" s="14"/>
       <c r="C231" s="30">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D231" s="28"/>
@@ -31063,7 +30729,6 @@
       <c r="A232" s="35"/>
       <c r="B232" s="14"/>
       <c r="C232" s="30">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D232" s="28"/>
@@ -31191,7 +30856,6 @@
       <c r="A233" s="35"/>
       <c r="B233" s="14"/>
       <c r="C233" s="30">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D233" s="28"/>
@@ -31319,7 +30983,6 @@
       <c r="A234" s="35"/>
       <c r="B234" s="14"/>
       <c r="C234" s="30">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D234" s="28"/>
@@ -31447,7 +31110,6 @@
       <c r="A235" s="35"/>
       <c r="B235" s="14"/>
       <c r="C235" s="30">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D235" s="28"/>
@@ -31575,7 +31237,6 @@
       <c r="A236" s="35"/>
       <c r="B236" s="14"/>
       <c r="C236" s="30">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D236" s="28"/>
@@ -31703,7 +31364,6 @@
       <c r="A237" s="35"/>
       <c r="B237" s="14"/>
       <c r="C237" s="30">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D237" s="28"/>
@@ -31831,7 +31491,6 @@
       <c r="A238" s="35"/>
       <c r="B238" s="14"/>
       <c r="C238" s="30">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D238" s="28"/>
@@ -31959,7 +31618,6 @@
       <c r="A239" s="35"/>
       <c r="B239" s="14"/>
       <c r="C239" s="30">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D239" s="28"/>
@@ -32087,7 +31745,6 @@
       <c r="A240" s="35"/>
       <c r="B240" s="14"/>
       <c r="C240" s="30">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D240" s="28"/>
@@ -32215,7 +31872,6 @@
       <c r="A241" s="35"/>
       <c r="B241" s="14"/>
       <c r="C241" s="30">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D241" s="28"/>
@@ -32343,7 +31999,6 @@
       <c r="A242" s="35"/>
       <c r="B242" s="14"/>
       <c r="C242" s="30">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D242" s="28"/>
@@ -32471,7 +32126,6 @@
       <c r="A243" s="35"/>
       <c r="B243" s="14"/>
       <c r="C243" s="30">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D243" s="28"/>
@@ -32599,7 +32253,6 @@
       <c r="A244" s="35"/>
       <c r="B244" s="14"/>
       <c r="C244" s="30">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D244" s="28"/>
@@ -32727,7 +32380,6 @@
       <c r="A245" s="35"/>
       <c r="B245" s="14"/>
       <c r="C245" s="30">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D245" s="28"/>
@@ -32855,7 +32507,6 @@
       <c r="A246" s="35"/>
       <c r="B246" s="14"/>
       <c r="C246" s="30">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D246" s="28"/>
@@ -32983,7 +32634,6 @@
       <c r="A247" s="35"/>
       <c r="B247" s="14"/>
       <c r="C247" s="30">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D247" s="28"/>
@@ -33111,7 +32761,6 @@
       <c r="A248" s="35"/>
       <c r="B248" s="14"/>
       <c r="C248" s="30">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D248" s="28"/>
@@ -33239,7 +32888,6 @@
       <c r="A249" s="35"/>
       <c r="B249" s="14"/>
       <c r="C249" s="30">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D249" s="28"/>
@@ -33367,7 +33015,6 @@
       <c r="A250" s="35"/>
       <c r="B250" s="14"/>
       <c r="C250" s="30">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D250" s="28"/>
@@ -33495,7 +33142,6 @@
       <c r="A251" s="35"/>
       <c r="B251" s="14"/>
       <c r="C251" s="30">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D251" s="28"/>
@@ -33623,7 +33269,6 @@
       <c r="A252" s="35"/>
       <c r="B252" s="14"/>
       <c r="C252" s="30">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D252" s="28"/>
@@ -33751,7 +33396,6 @@
       <c r="A253" s="35"/>
       <c r="B253" s="14"/>
       <c r="C253" s="30">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D253" s="28"/>
@@ -33879,7 +33523,6 @@
       <c r="A254" s="35"/>
       <c r="B254" s="14"/>
       <c r="C254" s="30">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D254" s="28"/>
@@ -34007,7 +33650,6 @@
       <c r="A255" s="35"/>
       <c r="B255" s="14"/>
       <c r="C255" s="30">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D255" s="28"/>
@@ -34135,7 +33777,6 @@
       <c r="A256" s="35"/>
       <c r="B256" s="14"/>
       <c r="C256" s="30">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D256" s="28"/>
@@ -34263,7 +33904,6 @@
       <c r="A257" s="35"/>
       <c r="B257" s="14"/>
       <c r="C257" s="30">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D257" s="28"/>
@@ -34391,7 +34031,6 @@
       <c r="A258" s="35"/>
       <c r="B258" s="14"/>
       <c r="C258" s="30">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D258" s="28"/>
@@ -34519,7 +34158,6 @@
       <c r="A259" s="35"/>
       <c r="B259" s="14"/>
       <c r="C259" s="30">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D259" s="28"/>
@@ -34647,7 +34285,6 @@
       <c r="A260" s="35"/>
       <c r="B260" s="14"/>
       <c r="C260" s="30">
-        <f t="shared" ref="C260:C299" si="4">SUM(D260:DS260)</f>
         <v>0</v>
       </c>
       <c r="D260" s="28"/>
@@ -34775,7 +34412,6 @@
       <c r="A261" s="35"/>
       <c r="B261" s="14"/>
       <c r="C261" s="30">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D261" s="28"/>
@@ -34903,7 +34539,6 @@
       <c r="A262" s="35"/>
       <c r="B262" s="14"/>
       <c r="C262" s="30">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D262" s="28"/>
@@ -35031,7 +34666,6 @@
       <c r="A263" s="35"/>
       <c r="B263" s="14"/>
       <c r="C263" s="30">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D263" s="28"/>
@@ -35159,7 +34793,6 @@
       <c r="A264" s="35"/>
       <c r="B264" s="14"/>
       <c r="C264" s="30">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D264" s="28"/>
@@ -35287,7 +34920,6 @@
       <c r="A265" s="35"/>
       <c r="B265" s="14"/>
       <c r="C265" s="30">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D265" s="28"/>
@@ -35415,7 +35047,6 @@
       <c r="A266" s="35"/>
       <c r="B266" s="14"/>
       <c r="C266" s="30">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D266" s="28"/>
@@ -35543,7 +35174,6 @@
       <c r="A267" s="35"/>
       <c r="B267" s="14"/>
       <c r="C267" s="30">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D267" s="28"/>
@@ -35671,7 +35301,6 @@
       <c r="A268" s="35"/>
       <c r="B268" s="14"/>
       <c r="C268" s="30">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D268" s="28"/>
@@ -35799,7 +35428,6 @@
       <c r="A269" s="35"/>
       <c r="B269" s="14"/>
       <c r="C269" s="30">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D269" s="28"/>
@@ -35927,7 +35555,6 @@
       <c r="A270" s="35"/>
       <c r="B270" s="14"/>
       <c r="C270" s="30">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D270" s="28"/>
@@ -36055,7 +35682,6 @@
       <c r="A271" s="35"/>
       <c r="B271" s="14"/>
       <c r="C271" s="30">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D271" s="28"/>
@@ -36183,7 +35809,6 @@
       <c r="A272" s="35"/>
       <c r="B272" s="14"/>
       <c r="C272" s="30">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D272" s="28"/>
@@ -36311,7 +35936,6 @@
       <c r="A273" s="35"/>
       <c r="B273" s="14"/>
       <c r="C273" s="30">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D273" s="28"/>
@@ -36439,7 +36063,6 @@
       <c r="A274" s="35"/>
       <c r="B274" s="14"/>
       <c r="C274" s="30">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D274" s="28"/>
@@ -36567,7 +36190,6 @@
       <c r="A275" s="35"/>
       <c r="B275" s="14"/>
       <c r="C275" s="30">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D275" s="28"/>
@@ -36695,7 +36317,6 @@
       <c r="A276" s="35"/>
       <c r="B276" s="14"/>
       <c r="C276" s="30">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D276" s="28"/>
@@ -36823,7 +36444,6 @@
       <c r="A277" s="35"/>
       <c r="B277" s="14"/>
       <c r="C277" s="30">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D277" s="28"/>
@@ -36951,7 +36571,6 @@
       <c r="A278" s="35"/>
       <c r="B278" s="14"/>
       <c r="C278" s="30">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D278" s="28"/>
@@ -37079,7 +36698,6 @@
       <c r="A279" s="35"/>
       <c r="B279" s="14"/>
       <c r="C279" s="30">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D279" s="28"/>
@@ -37207,7 +36825,6 @@
       <c r="A280" s="35"/>
       <c r="B280" s="14"/>
       <c r="C280" s="30">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D280" s="28"/>
@@ -37335,7 +36952,6 @@
       <c r="A281" s="35"/>
       <c r="B281" s="14"/>
       <c r="C281" s="30">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D281" s="28"/>
@@ -37463,7 +37079,6 @@
       <c r="A282" s="35"/>
       <c r="B282" s="14"/>
       <c r="C282" s="30">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D282" s="28"/>
@@ -37591,7 +37206,6 @@
       <c r="A283" s="35"/>
       <c r="B283" s="14"/>
       <c r="C283" s="30">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D283" s="28"/>
@@ -37719,7 +37333,6 @@
       <c r="A284" s="35"/>
       <c r="B284" s="14"/>
       <c r="C284" s="30">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D284" s="28"/>
@@ -37847,7 +37460,6 @@
       <c r="A285" s="35"/>
       <c r="B285" s="14"/>
       <c r="C285" s="30">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D285" s="28"/>
@@ -37975,7 +37587,6 @@
       <c r="A286" s="35"/>
       <c r="B286" s="14"/>
       <c r="C286" s="30">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D286" s="28"/>
@@ -38103,7 +37714,6 @@
       <c r="A287" s="35"/>
       <c r="B287" s="14"/>
       <c r="C287" s="30">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D287" s="28"/>
@@ -38231,7 +37841,6 @@
       <c r="A288" s="35"/>
       <c r="B288" s="14"/>
       <c r="C288" s="30">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D288" s="28"/>
@@ -38359,7 +37968,6 @@
       <c r="A289" s="35"/>
       <c r="B289" s="14"/>
       <c r="C289" s="30">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D289" s="28"/>
@@ -38487,7 +38095,6 @@
       <c r="A290" s="35"/>
       <c r="B290" s="14"/>
       <c r="C290" s="30">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D290" s="28"/>
@@ -38615,7 +38222,6 @@
       <c r="A291" s="35"/>
       <c r="B291" s="14"/>
       <c r="C291" s="30">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D291" s="28"/>
@@ -38743,7 +38349,6 @@
       <c r="A292" s="35"/>
       <c r="B292" s="14"/>
       <c r="C292" s="30">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D292" s="28"/>
@@ -38871,7 +38476,6 @@
       <c r="A293" s="35"/>
       <c r="B293" s="14"/>
       <c r="C293" s="30">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D293" s="28"/>
@@ -38999,7 +38603,6 @@
       <c r="A294" s="35"/>
       <c r="B294" s="14"/>
       <c r="C294" s="30">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D294" s="28"/>
@@ -39127,7 +38730,6 @@
       <c r="A295" s="35"/>
       <c r="B295" s="14"/>
       <c r="C295" s="30">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D295" s="28"/>
@@ -39255,7 +38857,6 @@
       <c r="A296" s="35"/>
       <c r="B296" s="14"/>
       <c r="C296" s="30">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D296" s="28"/>
@@ -39383,7 +38984,6 @@
       <c r="A297" s="35"/>
       <c r="B297" s="14"/>
       <c r="C297" s="30">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D297" s="28"/>
@@ -39511,7 +39111,6 @@
       <c r="A298" s="35"/>
       <c r="B298" s="14"/>
       <c r="C298" s="30">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D298" s="28"/>
@@ -39639,7 +39238,6 @@
       <c r="A299" s="36"/>
       <c r="B299" s="18"/>
       <c r="C299" s="31">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D299" s="29"/>
@@ -39768,6 +39366,19 @@
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="AD1:AF1"/>
+    <mergeCell ref="BX2:CA2"/>
+    <mergeCell ref="CJ2:CM2"/>
+    <mergeCell ref="AG1:AK1"/>
+    <mergeCell ref="Z1:AC1"/>
+    <mergeCell ref="BT1:BW1"/>
+    <mergeCell ref="AL1:AO1"/>
+    <mergeCell ref="CV2:CY2"/>
+    <mergeCell ref="AT1:AW1"/>
+    <mergeCell ref="BB1:BG1"/>
+    <mergeCell ref="DH2:DK2"/>
+    <mergeCell ref="BH1:BM1"/>
+    <mergeCell ref="BN1:BS1"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="DP2:DS2"/>
     <mergeCell ref="AX1:BA1"/>
@@ -39784,19 +39395,6 @@
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="N1:Q1"/>
     <mergeCell ref="U1:Y1"/>
-    <mergeCell ref="CV2:CY2"/>
-    <mergeCell ref="AT1:AW1"/>
-    <mergeCell ref="BB1:BG1"/>
-    <mergeCell ref="DH2:DK2"/>
-    <mergeCell ref="BH1:BM1"/>
-    <mergeCell ref="BN1:BS1"/>
-    <mergeCell ref="AD1:AF1"/>
-    <mergeCell ref="BX2:CA2"/>
-    <mergeCell ref="CJ2:CM2"/>
-    <mergeCell ref="AG1:AK1"/>
-    <mergeCell ref="Z1:AC1"/>
-    <mergeCell ref="BT1:BW1"/>
-    <mergeCell ref="AL1:AO1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
